--- a/dev/energyscope_data/CA-QC/unit_conversion.xlsx
+++ b/dev/energyscope_data/CA-QC/unit_conversion.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\PycharmProjects\energyscope-lca\01_Notebooks\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\PycharmProjects\EnergyScope-Quebec\projects\lca\02_Regionalization\01_Notebooks\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBAEE17-B706-452C-836A-804CFC196769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953C6B13-0CE0-4D1F-B6B6-E6A203DB506B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$1319</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$1318</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6221" uniqueCount="1046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6276" uniqueCount="1045">
   <si>
     <t>Name</t>
   </si>
@@ -2463,9 +2463,6 @@
     <t>payload (6.3 t), yearly distance (73000 km): \cite{sacchi2021}, capacity factor (0.093): \cite{limpens2021}</t>
   </si>
   <si>
-    <t>natural gas LHV (13.1 kWh/kg), natural gas density (0.777 kg/m3): \cite{engineeringtoolbox2003}</t>
-  </si>
-  <si>
     <t>annual output (130 kt/y): \cite{wernet2016}, capacity factor (0.85): \cite{moret2017}</t>
   </si>
   <si>
@@ -3138,18 +3135,6 @@
     <t>Existing grid length (108096 km), corresponding grid capacity (21.45 GW): \cite{hydro-quebec2023}</t>
   </si>
   <si>
-    <t>Existing grid length (789 km), corresponding grid capacity (9.76 GW): data from private communications with Energir</t>
-  </si>
-  <si>
-    <t>Existing grid length (76 km), corresponding grid capacity (9.76 GW): data from private communications with Energir</t>
-  </si>
-  <si>
-    <t>Existing grid length (7560 km), corresponding grid capacity (5.05 GW): data from private communications with Energir</t>
-  </si>
-  <si>
-    <t>Existing grid length (1966 km), corresponding grid capacity (9.74 GW): data from private communications with Energir</t>
-  </si>
-  <si>
     <t>payload (13.4 t), yearly distance (108000 km): \cite{sacchi2021}, capacity factor (0.093): \cite{limpens2021}</t>
   </si>
   <si>
@@ -3175,6 +3160,18 @@
   </si>
   <si>
     <t>corn energy content (13.622 MJ/kg): \cite{sacchi2022}</t>
+  </si>
+  <si>
+    <t>Existing grid length (789 km), corresponding grid capacity (9.76 GW): data from communications with Energir</t>
+  </si>
+  <si>
+    <t>Existing grid length (76 km), corresponding grid capacity (9.76 GW): data from communications with Energir</t>
+  </si>
+  <si>
+    <t>Existing grid length (7560 km), corresponding grid capacity (5.05 GW): data from communications with Energir</t>
+  </si>
+  <si>
+    <t>Existing grid length (1966 km), corresponding grid capacity (9.74 GW): data from communications with Energir</t>
   </si>
 </sst>
 </file>
@@ -3544,7 +3541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1319"/>
+  <dimension ref="A1:F1318"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.453125" bestFit="1" customWidth="1"/>
@@ -3633,7 +3630,7 @@
         <v>730</v>
       </c>
       <c r="F4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -3671,7 +3668,7 @@
         <v>730</v>
       </c>
       <c r="F6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -3857,7 +3854,7 @@
         <v>730</v>
       </c>
       <c r="F16" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -3878,7 +3875,7 @@
         <v>723</v>
       </c>
       <c r="F17" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -3937,7 +3934,7 @@
         <v>730</v>
       </c>
       <c r="F20" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -4341,7 +4338,7 @@
         <v>730</v>
       </c>
       <c r="F40" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -4362,7 +4359,7 @@
         <v>723</v>
       </c>
       <c r="F41" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -4543,7 +4540,7 @@
         <v>730</v>
       </c>
       <c r="F50" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -4585,7 +4582,7 @@
         <v>730</v>
       </c>
       <c r="F52" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -4703,7 +4700,7 @@
         <v>730</v>
       </c>
       <c r="F58" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4745,7 +4742,7 @@
         <v>730</v>
       </c>
       <c r="F60" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
@@ -5256,7 +5253,7 @@
         <v>725</v>
       </c>
       <c r="F86" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
@@ -5298,7 +5295,7 @@
         <v>725</v>
       </c>
       <c r="F88" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
@@ -5340,7 +5337,7 @@
         <v>725</v>
       </c>
       <c r="F90" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
@@ -5382,7 +5379,7 @@
         <v>725</v>
       </c>
       <c r="F92" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
@@ -5424,7 +5421,7 @@
         <v>725</v>
       </c>
       <c r="F94" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
@@ -5466,7 +5463,7 @@
         <v>725</v>
       </c>
       <c r="F96" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
@@ -5508,7 +5505,7 @@
         <v>725</v>
       </c>
       <c r="F98" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
@@ -5550,7 +5547,7 @@
         <v>725</v>
       </c>
       <c r="F100" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
@@ -5592,7 +5589,7 @@
         <v>725</v>
       </c>
       <c r="F102" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -5634,7 +5631,7 @@
         <v>725</v>
       </c>
       <c r="F104" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
@@ -5676,7 +5673,7 @@
         <v>725</v>
       </c>
       <c r="F106" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
@@ -5718,7 +5715,7 @@
         <v>725</v>
       </c>
       <c r="F108" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -5760,7 +5757,7 @@
         <v>725</v>
       </c>
       <c r="F110" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -5802,7 +5799,7 @@
         <v>725</v>
       </c>
       <c r="F112" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
@@ -5844,7 +5841,7 @@
         <v>725</v>
       </c>
       <c r="F114" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
@@ -5886,7 +5883,7 @@
         <v>725</v>
       </c>
       <c r="F116" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
@@ -5928,7 +5925,7 @@
         <v>725</v>
       </c>
       <c r="F118" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
@@ -5970,7 +5967,7 @@
         <v>725</v>
       </c>
       <c r="F120" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
@@ -6012,7 +6009,7 @@
         <v>725</v>
       </c>
       <c r="F122" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
@@ -6054,7 +6051,7 @@
         <v>725</v>
       </c>
       <c r="F124" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -6096,7 +6093,7 @@
         <v>725</v>
       </c>
       <c r="F126" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -6138,7 +6135,7 @@
         <v>725</v>
       </c>
       <c r="F128" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -6180,7 +6177,7 @@
         <v>725</v>
       </c>
       <c r="F130" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.35">
@@ -6222,7 +6219,7 @@
         <v>725</v>
       </c>
       <c r="F132" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
@@ -6264,7 +6261,7 @@
         <v>725</v>
       </c>
       <c r="F134" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
@@ -6306,7 +6303,7 @@
         <v>725</v>
       </c>
       <c r="F136" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
@@ -6348,7 +6345,7 @@
         <v>725</v>
       </c>
       <c r="F138" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
@@ -6390,7 +6387,7 @@
         <v>725</v>
       </c>
       <c r="F140" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
@@ -6432,7 +6429,7 @@
         <v>725</v>
       </c>
       <c r="F142" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
@@ -6474,7 +6471,7 @@
         <v>725</v>
       </c>
       <c r="F144" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
@@ -6516,7 +6513,7 @@
         <v>725</v>
       </c>
       <c r="F146" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
@@ -6558,7 +6555,7 @@
         <v>725</v>
       </c>
       <c r="F148" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
@@ -6600,7 +6597,7 @@
         <v>725</v>
       </c>
       <c r="F150" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
@@ -6642,7 +6639,7 @@
         <v>725</v>
       </c>
       <c r="F152" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
@@ -6684,7 +6681,7 @@
         <v>725</v>
       </c>
       <c r="F154" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.35">
@@ -6726,7 +6723,7 @@
         <v>725</v>
       </c>
       <c r="F156" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
@@ -6768,7 +6765,7 @@
         <v>725</v>
       </c>
       <c r="F158" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.35">
@@ -6810,7 +6807,7 @@
         <v>725</v>
       </c>
       <c r="F160" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.35">
@@ -6852,7 +6849,7 @@
         <v>725</v>
       </c>
       <c r="F162" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.35">
@@ -6894,7 +6891,7 @@
         <v>725</v>
       </c>
       <c r="F164" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
@@ -6936,7 +6933,7 @@
         <v>725</v>
       </c>
       <c r="F166" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
@@ -6978,7 +6975,7 @@
         <v>725</v>
       </c>
       <c r="F168" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.35">
@@ -7020,7 +7017,7 @@
         <v>725</v>
       </c>
       <c r="F170" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.35">
@@ -7062,7 +7059,7 @@
         <v>725</v>
       </c>
       <c r="F172" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
@@ -7104,7 +7101,7 @@
         <v>725</v>
       </c>
       <c r="F174" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.35">
@@ -7146,7 +7143,7 @@
         <v>725</v>
       </c>
       <c r="F176" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.35">
@@ -7188,7 +7185,7 @@
         <v>725</v>
       </c>
       <c r="F178" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
@@ -7230,7 +7227,7 @@
         <v>725</v>
       </c>
       <c r="F180" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.35">
@@ -7272,7 +7269,7 @@
         <v>725</v>
       </c>
       <c r="F182" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.35">
@@ -7314,7 +7311,7 @@
         <v>725</v>
       </c>
       <c r="F184" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.35">
@@ -7356,7 +7353,7 @@
         <v>725</v>
       </c>
       <c r="F186" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.35">
@@ -7398,7 +7395,7 @@
         <v>725</v>
       </c>
       <c r="F188" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.35">
@@ -7419,7 +7416,7 @@
         <v>730</v>
       </c>
       <c r="F189" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.35">
@@ -7458,7 +7455,7 @@
         <v>730</v>
       </c>
       <c r="F191" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.35">
@@ -7653,7 +7650,7 @@
         <v>723</v>
       </c>
       <c r="F201" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
@@ -7695,7 +7692,7 @@
         <v>723</v>
       </c>
       <c r="F203" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
@@ -9110,7 +9107,7 @@
         <v>730</v>
       </c>
       <c r="F275" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.35">
@@ -9149,7 +9146,7 @@
         <v>730</v>
       </c>
       <c r="F277" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.35">
@@ -9188,7 +9185,7 @@
         <v>730</v>
       </c>
       <c r="F279" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.35">
@@ -9226,7 +9223,7 @@
         <v>730</v>
       </c>
       <c r="F281" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.35">
@@ -9248,7 +9245,7 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B283" t="s">
         <v>718</v>
@@ -9264,12 +9261,12 @@
         <v>732</v>
       </c>
       <c r="F283" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B284" t="s">
         <v>719</v>
@@ -9286,7 +9283,7 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B285" t="s">
         <v>718</v>
@@ -9302,12 +9299,12 @@
         <v>732</v>
       </c>
       <c r="F285" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B286" t="s">
         <v>719</v>
@@ -9340,7 +9337,7 @@
         <v>732</v>
       </c>
       <c r="F287" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.35">
@@ -9378,7 +9375,7 @@
         <v>732</v>
       </c>
       <c r="F289" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.35">
@@ -9416,7 +9413,7 @@
         <v>730</v>
       </c>
       <c r="F291" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
@@ -9437,7 +9434,7 @@
         <v>723</v>
       </c>
       <c r="F292" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
@@ -9458,7 +9455,7 @@
         <v>730</v>
       </c>
       <c r="F293" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
@@ -9500,7 +9497,7 @@
         <v>730</v>
       </c>
       <c r="F295" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.35">
@@ -9521,7 +9518,7 @@
         <v>723</v>
       </c>
       <c r="F296" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.35">
@@ -9542,7 +9539,7 @@
         <v>731</v>
       </c>
       <c r="F297" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.35">
@@ -9615,7 +9612,7 @@
         <v>731</v>
       </c>
       <c r="F301" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.35">
@@ -9688,7 +9685,7 @@
         <v>730</v>
       </c>
       <c r="F305" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
@@ -9709,7 +9706,7 @@
         <v>723</v>
       </c>
       <c r="F306" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
@@ -9730,7 +9727,7 @@
         <v>730</v>
       </c>
       <c r="F307" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
@@ -9769,7 +9766,7 @@
         <v>730</v>
       </c>
       <c r="F309" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
@@ -9846,7 +9843,7 @@
         <v>730</v>
       </c>
       <c r="F313" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.35">
@@ -9885,7 +9882,7 @@
         <v>730</v>
       </c>
       <c r="F315" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
@@ -9906,7 +9903,7 @@
         <v>723</v>
       </c>
       <c r="F316" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
@@ -9978,7 +9975,7 @@
         <v>730</v>
       </c>
       <c r="F320" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
@@ -10055,7 +10052,7 @@
         <v>722</v>
       </c>
       <c r="F324" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
@@ -10076,7 +10073,7 @@
         <v>730</v>
       </c>
       <c r="F325" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
@@ -10132,7 +10129,7 @@
         <v>722</v>
       </c>
       <c r="F328" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
@@ -10153,7 +10150,7 @@
         <v>730</v>
       </c>
       <c r="F329" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
@@ -10191,7 +10188,7 @@
         <v>730</v>
       </c>
       <c r="F331" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
@@ -10251,7 +10248,7 @@
         <v>730</v>
       </c>
       <c r="F334" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
@@ -10328,7 +10325,7 @@
         <v>730</v>
       </c>
       <c r="F338" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
@@ -10483,7 +10480,7 @@
         <v>730</v>
       </c>
       <c r="F346" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.35">
@@ -10556,7 +10553,7 @@
         <v>730</v>
       </c>
       <c r="F350" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
@@ -10577,7 +10574,7 @@
         <v>723</v>
       </c>
       <c r="F351" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
@@ -10649,7 +10646,7 @@
         <v>730</v>
       </c>
       <c r="F355" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.35">
@@ -10709,7 +10706,7 @@
         <v>730</v>
       </c>
       <c r="F358" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
@@ -10809,7 +10806,7 @@
         <v>730</v>
       </c>
       <c r="F363" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
@@ -10830,7 +10827,7 @@
         <v>723</v>
       </c>
       <c r="F364" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
@@ -10885,7 +10882,7 @@
         <v>722</v>
       </c>
       <c r="F367" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
@@ -10906,7 +10903,7 @@
         <v>730</v>
       </c>
       <c r="F368" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
@@ -10945,7 +10942,7 @@
         <v>730</v>
       </c>
       <c r="F370" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
@@ -10984,7 +10981,7 @@
         <v>730</v>
       </c>
       <c r="F372" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
@@ -11026,7 +11023,7 @@
         <v>723</v>
       </c>
       <c r="F374" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.35">
@@ -11081,7 +11078,7 @@
         <v>730</v>
       </c>
       <c r="F377" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
@@ -11221,7 +11218,7 @@
         <v>723</v>
       </c>
       <c r="F384" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.35">
@@ -11305,7 +11302,7 @@
         <v>723</v>
       </c>
       <c r="F388" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
@@ -11604,7 +11601,7 @@
         <v>723</v>
       </c>
       <c r="F403" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
@@ -11625,7 +11622,7 @@
         <v>730</v>
       </c>
       <c r="F404" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
@@ -11705,7 +11702,7 @@
         <v>730</v>
       </c>
       <c r="F408" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
@@ -11806,7 +11803,7 @@
         <v>723</v>
       </c>
       <c r="F413" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.35">
@@ -11827,7 +11824,7 @@
         <v>730</v>
       </c>
       <c r="F414" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.35">
@@ -11865,7 +11862,7 @@
         <v>730</v>
       </c>
       <c r="F416" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.35">
@@ -11904,7 +11901,7 @@
         <v>730</v>
       </c>
       <c r="F418" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.35">
@@ -11946,7 +11943,7 @@
         <v>730</v>
       </c>
       <c r="F420" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.35">
@@ -11988,7 +11985,7 @@
         <v>730</v>
       </c>
       <c r="F422" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.35">
@@ -12072,7 +12069,7 @@
         <v>730</v>
       </c>
       <c r="F426" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.35">
@@ -12135,7 +12132,7 @@
         <v>730</v>
       </c>
       <c r="F429" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.35">
@@ -12198,7 +12195,7 @@
         <v>730</v>
       </c>
       <c r="F432" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
@@ -12303,7 +12300,7 @@
         <v>730</v>
       </c>
       <c r="F437" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
@@ -12342,7 +12339,7 @@
         <v>730</v>
       </c>
       <c r="F439" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
@@ -12420,7 +12417,7 @@
         <v>730</v>
       </c>
       <c r="F443" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.35">
@@ -12441,7 +12438,7 @@
         <v>730</v>
       </c>
       <c r="F444" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.35">
@@ -12480,7 +12477,7 @@
         <v>730</v>
       </c>
       <c r="F446" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.35">
@@ -12501,7 +12498,7 @@
         <v>723</v>
       </c>
       <c r="F447" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.35">
@@ -12522,7 +12519,7 @@
         <v>730</v>
       </c>
       <c r="F448" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.35">
@@ -12564,7 +12561,7 @@
         <v>722</v>
       </c>
       <c r="F450" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.35">
@@ -12602,7 +12599,7 @@
         <v>730</v>
       </c>
       <c r="F452" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.35">
@@ -12641,7 +12638,7 @@
         <v>730</v>
       </c>
       <c r="F454" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.35">
@@ -12680,7 +12677,7 @@
         <v>730</v>
       </c>
       <c r="F456" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.35">
@@ -12719,7 +12716,7 @@
         <v>730</v>
       </c>
       <c r="F458" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.35">
@@ -12796,7 +12793,7 @@
         <v>730</v>
       </c>
       <c r="F462" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.35">
@@ -12835,7 +12832,7 @@
         <v>730</v>
       </c>
       <c r="F464" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.35">
@@ -12874,7 +12871,7 @@
         <v>730</v>
       </c>
       <c r="F466" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.35">
@@ -12913,7 +12910,7 @@
         <v>730</v>
       </c>
       <c r="F468" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.35">
@@ -12934,7 +12931,7 @@
         <v>723</v>
       </c>
       <c r="F469" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.35">
@@ -13006,7 +13003,7 @@
         <v>730</v>
       </c>
       <c r="F473" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.35">
@@ -13045,7 +13042,7 @@
         <v>730</v>
       </c>
       <c r="F475" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.35">
@@ -13166,7 +13163,7 @@
         <v>730</v>
       </c>
       <c r="F481" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.35">
@@ -13187,7 +13184,7 @@
         <v>723</v>
       </c>
       <c r="F482" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.35">
@@ -13259,7 +13256,7 @@
         <v>730</v>
       </c>
       <c r="F486" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.35">
@@ -13297,7 +13294,7 @@
         <v>730</v>
       </c>
       <c r="F488" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.35">
@@ -13378,7 +13375,7 @@
         <v>729</v>
       </c>
       <c r="F492" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.35">
@@ -13420,7 +13417,7 @@
         <v>729</v>
       </c>
       <c r="F494" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.35">
@@ -13462,7 +13459,7 @@
         <v>729</v>
       </c>
       <c r="F496" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.35">
@@ -13504,7 +13501,7 @@
         <v>729</v>
       </c>
       <c r="F498" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.35">
@@ -13546,7 +13543,7 @@
         <v>729</v>
       </c>
       <c r="F500" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.35">
@@ -13588,7 +13585,7 @@
         <v>729</v>
       </c>
       <c r="F502" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.35">
@@ -13630,7 +13627,7 @@
         <v>729</v>
       </c>
       <c r="F504" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.35">
@@ -13672,7 +13669,7 @@
         <v>729</v>
       </c>
       <c r="F506" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.35">
@@ -13714,7 +13711,7 @@
         <v>729</v>
       </c>
       <c r="F508" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.35">
@@ -13756,7 +13753,7 @@
         <v>729</v>
       </c>
       <c r="F510" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.35">
@@ -13798,7 +13795,7 @@
         <v>729</v>
       </c>
       <c r="F512" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.35">
@@ -13840,7 +13837,7 @@
         <v>729</v>
       </c>
       <c r="F514" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.35">
@@ -13882,7 +13879,7 @@
         <v>729</v>
       </c>
       <c r="F516" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.35">
@@ -13924,7 +13921,7 @@
         <v>729</v>
       </c>
       <c r="F518" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.35">
@@ -13966,7 +13963,7 @@
         <v>729</v>
       </c>
       <c r="F520" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.35">
@@ -14008,7 +14005,7 @@
         <v>729</v>
       </c>
       <c r="F522" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.35">
@@ -14050,7 +14047,7 @@
         <v>729</v>
       </c>
       <c r="F524" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.35">
@@ -14092,7 +14089,7 @@
         <v>729</v>
       </c>
       <c r="F526" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.35">
@@ -14155,7 +14152,7 @@
         <v>730</v>
       </c>
       <c r="F529" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.35">
@@ -14197,7 +14194,7 @@
         <v>723</v>
       </c>
       <c r="F531" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.35">
@@ -14218,7 +14215,7 @@
         <v>730</v>
       </c>
       <c r="F532" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.35">
@@ -14281,7 +14278,7 @@
         <v>723</v>
       </c>
       <c r="F535" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.35">
@@ -14428,7 +14425,7 @@
         <v>723</v>
       </c>
       <c r="F542" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.35">
@@ -14470,7 +14467,7 @@
         <v>723</v>
       </c>
       <c r="F544" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.35">
@@ -14509,7 +14506,7 @@
         <v>730</v>
       </c>
       <c r="F546" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.35">
@@ -14530,7 +14527,7 @@
         <v>730</v>
       </c>
       <c r="F547" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.35">
@@ -14569,7 +14566,7 @@
         <v>730</v>
       </c>
       <c r="F549" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.35">
@@ -14608,7 +14605,7 @@
         <v>730</v>
       </c>
       <c r="F551" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.35">
@@ -14650,7 +14647,7 @@
         <v>730</v>
       </c>
       <c r="F553" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.35">
@@ -14692,7 +14689,7 @@
         <v>730</v>
       </c>
       <c r="F555" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.35">
@@ -14707,7 +14704,7 @@
         <v>7.7419354838709681E-2</v>
       </c>
       <c r="D556" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E556" t="s">
         <v>723</v>
@@ -14776,7 +14773,7 @@
         <v>730</v>
       </c>
       <c r="F559" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.35">
@@ -14839,7 +14836,7 @@
         <v>730</v>
       </c>
       <c r="F562" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.35">
@@ -14902,7 +14899,7 @@
         <v>730</v>
       </c>
       <c r="F565" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.35">
@@ -14917,7 +14914,7 @@
         <v>7.7419354838709681E-2</v>
       </c>
       <c r="D566" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E566" t="s">
         <v>723</v>
@@ -14934,8 +14931,8 @@
         <v>717</v>
       </c>
       <c r="C567">
-        <f>1 / (0.777 * 13.1)</f>
-        <v>9.8244373053533368E-2</v>
+        <f>1 * 3.6 / 39</f>
+        <v>9.2307692307692313E-2</v>
       </c>
       <c r="D567" t="s">
         <v>724</v>
@@ -14955,8 +14952,8 @@
         <v>717</v>
       </c>
       <c r="C568">
-        <f>1 / (0.777 * 13.1)</f>
-        <v>9.8244373053533368E-2</v>
+        <f>1 * 3.6 / 39</f>
+        <v>9.2307692307692313E-2</v>
       </c>
       <c r="D568" t="s">
         <v>724</v>
@@ -15007,7 +15004,7 @@
         <v>730</v>
       </c>
       <c r="F570" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.35">
@@ -15049,7 +15046,7 @@
         <v>730</v>
       </c>
       <c r="F572" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.35">
@@ -15191,7 +15188,7 @@
         <v>730</v>
       </c>
       <c r="F579" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.35">
@@ -15229,7 +15226,7 @@
         <v>730</v>
       </c>
       <c r="F581" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.35">
@@ -15250,7 +15247,7 @@
         <v>723</v>
       </c>
       <c r="F582" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.35">
@@ -15271,7 +15268,7 @@
         <v>730</v>
       </c>
       <c r="F583" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.35">
@@ -15292,7 +15289,7 @@
         <v>723</v>
       </c>
       <c r="F584" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.35">
@@ -15313,7 +15310,7 @@
         <v>730</v>
       </c>
       <c r="F585" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.35">
@@ -15484,7 +15481,7 @@
         <v>730</v>
       </c>
       <c r="F594" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.35">
@@ -15522,7 +15519,7 @@
         <v>730</v>
       </c>
       <c r="F596" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.35">
@@ -15926,7 +15923,7 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B618" t="s">
         <v>718</v>
@@ -15942,12 +15939,12 @@
         <v>730</v>
       </c>
       <c r="F618" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B619" t="s">
         <v>719</v>
@@ -15965,7 +15962,7 @@
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B620" t="s">
         <v>718</v>
@@ -15981,12 +15978,12 @@
         <v>730</v>
       </c>
       <c r="F620" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B621" t="s">
         <v>719</v>
@@ -16096,7 +16093,7 @@
         <v>723</v>
       </c>
       <c r="F626" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.35">
@@ -16468,7 +16465,7 @@
         <v>733</v>
       </c>
       <c r="F645" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.35">
@@ -16489,7 +16486,7 @@
         <v>729</v>
       </c>
       <c r="F646" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.35">
@@ -16510,7 +16507,7 @@
         <v>733</v>
       </c>
       <c r="F647" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.35">
@@ -16531,7 +16528,7 @@
         <v>729</v>
       </c>
       <c r="F648" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.35">
@@ -16552,7 +16549,7 @@
         <v>733</v>
       </c>
       <c r="F649" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.35">
@@ -16573,7 +16570,7 @@
         <v>729</v>
       </c>
       <c r="F650" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.35">
@@ -16594,7 +16591,7 @@
         <v>733</v>
       </c>
       <c r="F651" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.35">
@@ -16615,7 +16612,7 @@
         <v>729</v>
       </c>
       <c r="F652" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.35">
@@ -16636,7 +16633,7 @@
         <v>733</v>
       </c>
       <c r="F653" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.35">
@@ -16657,7 +16654,7 @@
         <v>729</v>
       </c>
       <c r="F654" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.35">
@@ -16678,7 +16675,7 @@
         <v>733</v>
       </c>
       <c r="F655" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.35">
@@ -16699,7 +16696,7 @@
         <v>729</v>
       </c>
       <c r="F656" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.35">
@@ -16720,7 +16717,7 @@
         <v>733</v>
       </c>
       <c r="F657" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.35">
@@ -16741,7 +16738,7 @@
         <v>729</v>
       </c>
       <c r="F658" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.35">
@@ -16762,7 +16759,7 @@
         <v>733</v>
       </c>
       <c r="F659" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.35">
@@ -16783,7 +16780,7 @@
         <v>729</v>
       </c>
       <c r="F660" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.35">
@@ -16804,7 +16801,7 @@
         <v>733</v>
       </c>
       <c r="F661" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.35">
@@ -16842,7 +16839,7 @@
         <v>733</v>
       </c>
       <c r="F663" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.35">
@@ -16880,7 +16877,7 @@
         <v>733</v>
       </c>
       <c r="F665" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.35">
@@ -16901,7 +16898,7 @@
         <v>729</v>
       </c>
       <c r="F666" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.35">
@@ -16922,7 +16919,7 @@
         <v>733</v>
       </c>
       <c r="F667" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.35">
@@ -16943,7 +16940,7 @@
         <v>729</v>
       </c>
       <c r="F668" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.35">
@@ -16964,7 +16961,7 @@
         <v>733</v>
       </c>
       <c r="F669" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.35">
@@ -16985,7 +16982,7 @@
         <v>729</v>
       </c>
       <c r="F670" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.35">
@@ -17006,7 +17003,7 @@
         <v>733</v>
       </c>
       <c r="F671" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.35">
@@ -17027,7 +17024,7 @@
         <v>729</v>
       </c>
       <c r="F672" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.35">
@@ -17048,7 +17045,7 @@
         <v>733</v>
       </c>
       <c r="F673" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.35">
@@ -17069,7 +17066,7 @@
         <v>729</v>
       </c>
       <c r="F674" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.35">
@@ -17090,7 +17087,7 @@
         <v>733</v>
       </c>
       <c r="F675" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.35">
@@ -17111,7 +17108,7 @@
         <v>729</v>
       </c>
       <c r="F676" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.35">
@@ -17153,7 +17150,7 @@
         <v>729</v>
       </c>
       <c r="F678" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.35">
@@ -17195,7 +17192,7 @@
         <v>729</v>
       </c>
       <c r="F680" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.35">
@@ -17237,7 +17234,7 @@
         <v>729</v>
       </c>
       <c r="F682" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.35">
@@ -17279,7 +17276,7 @@
         <v>729</v>
       </c>
       <c r="F684" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.35">
@@ -17321,7 +17318,7 @@
         <v>729</v>
       </c>
       <c r="F686" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.35">
@@ -17363,7 +17360,7 @@
         <v>729</v>
       </c>
       <c r="F688" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.35">
@@ -17405,7 +17402,7 @@
         <v>729</v>
       </c>
       <c r="F690" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.35">
@@ -17447,7 +17444,7 @@
         <v>729</v>
       </c>
       <c r="F692" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.35">
@@ -17656,8 +17653,8 @@
         <v>717</v>
       </c>
       <c r="C703">
-        <f>1 / (0.777 * 13.1)</f>
-        <v>9.8244373053533368E-2</v>
+        <f xml:space="preserve"> 3.6 / 39</f>
+        <v>9.2307692307692313E-2</v>
       </c>
       <c r="D703" t="s">
         <v>724</v>
@@ -17666,7 +17663,7 @@
         <v>723</v>
       </c>
       <c r="F703" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.35">
@@ -17677,8 +17674,8 @@
         <v>719</v>
       </c>
       <c r="C704">
-        <f>1 / (0.777 * 13.1)</f>
-        <v>9.8244373053533368E-2</v>
+        <f xml:space="preserve"> 3.6 / 39</f>
+        <v>9.2307692307692313E-2</v>
       </c>
       <c r="D704" t="s">
         <v>724</v>
@@ -17687,7 +17684,7 @@
         <v>723</v>
       </c>
       <c r="F704" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.35">
@@ -17708,7 +17705,7 @@
         <v>730</v>
       </c>
       <c r="F705" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.35">
@@ -17853,7 +17850,7 @@
         <v>731</v>
       </c>
       <c r="F713" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.35">
@@ -17891,7 +17888,7 @@
         <v>731</v>
       </c>
       <c r="F715" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.35">
@@ -17929,7 +17926,7 @@
         <v>731</v>
       </c>
       <c r="F717" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.35">
@@ -18034,14 +18031,17 @@
         <v>719</v>
       </c>
       <c r="C723">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D723" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E723" t="s">
         <v>725</v>
+      </c>
+      <c r="F723" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.35">
@@ -18073,14 +18073,17 @@
         <v>719</v>
       </c>
       <c r="C725">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D725" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E725" t="s">
         <v>725</v>
+      </c>
+      <c r="F725" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.35">
@@ -18112,14 +18115,17 @@
         <v>719</v>
       </c>
       <c r="C727">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D727" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E727" t="s">
         <v>725</v>
+      </c>
+      <c r="F727" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.35">
@@ -18151,14 +18157,17 @@
         <v>719</v>
       </c>
       <c r="C729">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D729" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E729" t="s">
         <v>725</v>
+      </c>
+      <c r="F729" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.35">
@@ -18190,14 +18199,17 @@
         <v>719</v>
       </c>
       <c r="C731">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D731" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E731" t="s">
         <v>725</v>
+      </c>
+      <c r="F731" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.35">
@@ -18229,14 +18241,17 @@
         <v>719</v>
       </c>
       <c r="C733">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D733" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E733" t="s">
         <v>725</v>
+      </c>
+      <c r="F733" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.35">
@@ -18268,14 +18283,17 @@
         <v>719</v>
       </c>
       <c r="C735">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D735" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E735" t="s">
         <v>725</v>
+      </c>
+      <c r="F735" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.35">
@@ -18307,14 +18325,17 @@
         <v>719</v>
       </c>
       <c r="C737">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D737" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E737" t="s">
         <v>725</v>
+      </c>
+      <c r="F737" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.35">
@@ -18346,14 +18367,17 @@
         <v>719</v>
       </c>
       <c r="C739">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D739" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E739" t="s">
         <v>725</v>
+      </c>
+      <c r="F739" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="740" spans="1:6" x14ac:dyDescent="0.35">
@@ -18385,14 +18409,17 @@
         <v>719</v>
       </c>
       <c r="C741">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D741" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E741" t="s">
         <v>725</v>
+      </c>
+      <c r="F741" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.35">
@@ -18424,14 +18451,17 @@
         <v>719</v>
       </c>
       <c r="C743">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D743" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E743" t="s">
         <v>725</v>
+      </c>
+      <c r="F743" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.35">
@@ -18463,14 +18493,17 @@
         <v>719</v>
       </c>
       <c r="C745">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D745" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E745" t="s">
         <v>725</v>
+      </c>
+      <c r="F745" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.35">
@@ -18502,14 +18535,17 @@
         <v>719</v>
       </c>
       <c r="C747">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D747" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E747" t="s">
         <v>725</v>
+      </c>
+      <c r="F747" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.35">
@@ -18541,14 +18577,17 @@
         <v>719</v>
       </c>
       <c r="C749">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D749" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E749" t="s">
         <v>725</v>
+      </c>
+      <c r="F749" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.35">
@@ -18580,14 +18619,17 @@
         <v>719</v>
       </c>
       <c r="C751">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D751" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E751" t="s">
         <v>725</v>
+      </c>
+      <c r="F751" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.35">
@@ -18619,14 +18661,17 @@
         <v>719</v>
       </c>
       <c r="C753">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D753" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E753" t="s">
         <v>725</v>
+      </c>
+      <c r="F753" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.35">
@@ -18658,14 +18703,17 @@
         <v>719</v>
       </c>
       <c r="C755">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D755" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E755" t="s">
         <v>725</v>
+      </c>
+      <c r="F755" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.35">
@@ -18697,14 +18745,17 @@
         <v>719</v>
       </c>
       <c r="C757">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D757" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E757" t="s">
         <v>725</v>
+      </c>
+      <c r="F757" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.35">
@@ -18736,14 +18787,17 @@
         <v>719</v>
       </c>
       <c r="C759">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D759" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E759" t="s">
         <v>725</v>
+      </c>
+      <c r="F759" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.35">
@@ -18775,14 +18829,17 @@
         <v>719</v>
       </c>
       <c r="C761">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D761" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E761" t="s">
         <v>725</v>
+      </c>
+      <c r="F761" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.35">
@@ -18814,14 +18871,17 @@
         <v>719</v>
       </c>
       <c r="C763">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D763" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E763" t="s">
         <v>725</v>
+      </c>
+      <c r="F763" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.35">
@@ -18853,14 +18913,17 @@
         <v>719</v>
       </c>
       <c r="C765">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D765" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E765" t="s">
         <v>725</v>
+      </c>
+      <c r="F765" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.35">
@@ -18892,14 +18955,17 @@
         <v>719</v>
       </c>
       <c r="C767">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D767" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E767" t="s">
         <v>725</v>
+      </c>
+      <c r="F767" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.35">
@@ -18931,14 +18997,17 @@
         <v>719</v>
       </c>
       <c r="C769">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D769" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E769" t="s">
         <v>725</v>
+      </c>
+      <c r="F769" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.35">
@@ -18970,14 +19039,17 @@
         <v>719</v>
       </c>
       <c r="C771">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D771" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E771" t="s">
         <v>725</v>
+      </c>
+      <c r="F771" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.35">
@@ -19009,14 +19081,17 @@
         <v>719</v>
       </c>
       <c r="C773">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D773" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E773" t="s">
         <v>725</v>
+      </c>
+      <c r="F773" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.35">
@@ -19048,14 +19123,17 @@
         <v>719</v>
       </c>
       <c r="C775">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D775" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E775" t="s">
         <v>725</v>
+      </c>
+      <c r="F775" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.35">
@@ -19087,14 +19165,17 @@
         <v>719</v>
       </c>
       <c r="C777">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D777" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E777" t="s">
         <v>725</v>
+      </c>
+      <c r="F777" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.35">
@@ -19126,14 +19207,17 @@
         <v>719</v>
       </c>
       <c r="C779">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D779" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E779" t="s">
         <v>725</v>
+      </c>
+      <c r="F779" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.35">
@@ -19165,14 +19249,17 @@
         <v>719</v>
       </c>
       <c r="C781">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D781" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E781" t="s">
         <v>725</v>
+      </c>
+      <c r="F781" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="782" spans="1:6" x14ac:dyDescent="0.35">
@@ -19204,14 +19291,17 @@
         <v>719</v>
       </c>
       <c r="C783">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D783" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E783" t="s">
         <v>725</v>
+      </c>
+      <c r="F783" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.35">
@@ -19243,14 +19333,17 @@
         <v>719</v>
       </c>
       <c r="C785">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D785" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E785" t="s">
         <v>725</v>
+      </c>
+      <c r="F785" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.35">
@@ -19282,14 +19375,17 @@
         <v>719</v>
       </c>
       <c r="C787">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D787" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E787" t="s">
         <v>725</v>
+      </c>
+      <c r="F787" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.35">
@@ -19321,14 +19417,17 @@
         <v>719</v>
       </c>
       <c r="C789">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D789" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E789" t="s">
         <v>725</v>
+      </c>
+      <c r="F789" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.35">
@@ -19360,14 +19459,17 @@
         <v>719</v>
       </c>
       <c r="C791">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D791" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E791" t="s">
         <v>725</v>
+      </c>
+      <c r="F791" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="792" spans="1:6" x14ac:dyDescent="0.35">
@@ -19399,14 +19501,17 @@
         <v>719</v>
       </c>
       <c r="C793">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D793" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E793" t="s">
         <v>725</v>
+      </c>
+      <c r="F793" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.35">
@@ -19438,14 +19543,17 @@
         <v>719</v>
       </c>
       <c r="C795">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D795" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E795" t="s">
         <v>725</v>
+      </c>
+      <c r="F795" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.35">
@@ -19477,14 +19585,17 @@
         <v>719</v>
       </c>
       <c r="C797">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D797" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E797" t="s">
         <v>725</v>
+      </c>
+      <c r="F797" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.35">
@@ -19516,14 +19627,17 @@
         <v>719</v>
       </c>
       <c r="C799">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D799" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E799" t="s">
         <v>725</v>
+      </c>
+      <c r="F799" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.35">
@@ -19555,14 +19669,17 @@
         <v>719</v>
       </c>
       <c r="C801">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D801" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E801" t="s">
         <v>725</v>
+      </c>
+      <c r="F801" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.35">
@@ -19594,14 +19711,17 @@
         <v>719</v>
       </c>
       <c r="C803">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D803" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E803" t="s">
         <v>725</v>
+      </c>
+      <c r="F803" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.35">
@@ -19633,14 +19753,17 @@
         <v>719</v>
       </c>
       <c r="C805">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D805" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E805" t="s">
         <v>725</v>
+      </c>
+      <c r="F805" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.35">
@@ -19672,14 +19795,17 @@
         <v>719</v>
       </c>
       <c r="C807">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D807" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E807" t="s">
         <v>725</v>
+      </c>
+      <c r="F807" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.35">
@@ -19711,14 +19837,17 @@
         <v>719</v>
       </c>
       <c r="C809">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D809" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E809" t="s">
         <v>725</v>
+      </c>
+      <c r="F809" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.35">
@@ -19750,14 +19879,17 @@
         <v>719</v>
       </c>
       <c r="C811">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D811" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E811" t="s">
         <v>725</v>
+      </c>
+      <c r="F811" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.35">
@@ -19789,14 +19921,17 @@
         <v>719</v>
       </c>
       <c r="C813">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D813" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E813" t="s">
         <v>725</v>
+      </c>
+      <c r="F813" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.35">
@@ -19828,14 +19963,17 @@
         <v>719</v>
       </c>
       <c r="C815">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D815" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E815" t="s">
         <v>725</v>
+      </c>
+      <c r="F815" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.35">
@@ -19867,14 +20005,17 @@
         <v>719</v>
       </c>
       <c r="C817">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D817" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E817" t="s">
         <v>725</v>
+      </c>
+      <c r="F817" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.35">
@@ -19895,7 +20036,7 @@
         <v>730</v>
       </c>
       <c r="F818" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.35">
@@ -19934,7 +20075,7 @@
         <v>723</v>
       </c>
       <c r="F820" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="821" spans="1:6" x14ac:dyDescent="0.35">
@@ -20057,7 +20198,7 @@
         <v>732</v>
       </c>
       <c r="F827" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="828" spans="1:6" x14ac:dyDescent="0.35">
@@ -20096,7 +20237,7 @@
         <v>732</v>
       </c>
       <c r="F829" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="830" spans="1:6" x14ac:dyDescent="0.35">
@@ -20135,7 +20276,7 @@
         <v>732</v>
       </c>
       <c r="F831" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.35">
@@ -20174,7 +20315,7 @@
         <v>732</v>
       </c>
       <c r="F833" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="834" spans="1:6" x14ac:dyDescent="0.35">
@@ -20213,7 +20354,7 @@
         <v>733</v>
       </c>
       <c r="F835" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="836" spans="1:6" x14ac:dyDescent="0.35">
@@ -20250,7 +20391,7 @@
         <v>722</v>
       </c>
       <c r="F837" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="838" spans="1:6" x14ac:dyDescent="0.35">
@@ -20270,7 +20411,7 @@
         <v>722</v>
       </c>
       <c r="F838" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="839" spans="1:6" x14ac:dyDescent="0.35">
@@ -20291,7 +20432,7 @@
         <v>733</v>
       </c>
       <c r="F839" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.35">
@@ -20328,7 +20469,7 @@
         <v>722</v>
       </c>
       <c r="F841" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.35">
@@ -20348,7 +20489,7 @@
         <v>722</v>
       </c>
       <c r="F842" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="843" spans="1:6" x14ac:dyDescent="0.35">
@@ -20369,7 +20510,7 @@
         <v>733</v>
       </c>
       <c r="F843" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="844" spans="1:6" x14ac:dyDescent="0.35">
@@ -20406,7 +20547,7 @@
         <v>722</v>
       </c>
       <c r="F845" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="846" spans="1:6" x14ac:dyDescent="0.35">
@@ -20426,7 +20567,7 @@
         <v>722</v>
       </c>
       <c r="F846" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="847" spans="1:6" x14ac:dyDescent="0.35">
@@ -20447,7 +20588,7 @@
         <v>733</v>
       </c>
       <c r="F847" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="848" spans="1:6" x14ac:dyDescent="0.35">
@@ -20484,7 +20625,7 @@
         <v>722</v>
       </c>
       <c r="F849" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="850" spans="1:6" x14ac:dyDescent="0.35">
@@ -20504,7 +20645,7 @@
         <v>722</v>
       </c>
       <c r="F850" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="851" spans="1:6" x14ac:dyDescent="0.35">
@@ -20525,7 +20666,7 @@
         <v>733</v>
       </c>
       <c r="F851" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.35">
@@ -20562,7 +20703,7 @@
         <v>722</v>
       </c>
       <c r="F853" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.35">
@@ -20582,7 +20723,7 @@
         <v>722</v>
       </c>
       <c r="F854" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.35">
@@ -20603,7 +20744,7 @@
         <v>733</v>
       </c>
       <c r="F855" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.35">
@@ -20641,7 +20782,7 @@
         <v>722</v>
       </c>
       <c r="F857" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.35">
@@ -20661,7 +20802,7 @@
         <v>722</v>
       </c>
       <c r="F858" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.35">
@@ -20682,7 +20823,7 @@
         <v>733</v>
       </c>
       <c r="F859" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.35">
@@ -20720,7 +20861,7 @@
         <v>722</v>
       </c>
       <c r="F861" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.35">
@@ -20740,7 +20881,7 @@
         <v>722</v>
       </c>
       <c r="F862" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.35">
@@ -20761,7 +20902,7 @@
         <v>733</v>
       </c>
       <c r="F863" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.35">
@@ -20798,7 +20939,7 @@
         <v>722</v>
       </c>
       <c r="F865" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.35">
@@ -20818,7 +20959,7 @@
         <v>722</v>
       </c>
       <c r="F866" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="867" spans="1:6" x14ac:dyDescent="0.35">
@@ -20839,7 +20980,7 @@
         <v>733</v>
       </c>
       <c r="F867" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="868" spans="1:6" x14ac:dyDescent="0.35">
@@ -20876,7 +21017,7 @@
         <v>722</v>
       </c>
       <c r="F869" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="870" spans="1:6" x14ac:dyDescent="0.35">
@@ -20896,7 +21037,7 @@
         <v>722</v>
       </c>
       <c r="F870" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="871" spans="1:6" x14ac:dyDescent="0.35">
@@ -20917,7 +21058,7 @@
         <v>733</v>
       </c>
       <c r="F871" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="872" spans="1:6" x14ac:dyDescent="0.35">
@@ -20954,7 +21095,7 @@
         <v>722</v>
       </c>
       <c r="F873" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.35">
@@ -20974,7 +21115,7 @@
         <v>722</v>
       </c>
       <c r="F874" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="875" spans="1:6" x14ac:dyDescent="0.35">
@@ -20995,7 +21136,7 @@
         <v>732</v>
       </c>
       <c r="F875" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="876" spans="1:6" x14ac:dyDescent="0.35">
@@ -21034,7 +21175,7 @@
         <v>732</v>
       </c>
       <c r="F877" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="878" spans="1:6" x14ac:dyDescent="0.35">
@@ -21073,7 +21214,7 @@
         <v>732</v>
       </c>
       <c r="F879" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="880" spans="1:6" x14ac:dyDescent="0.35">
@@ -21112,7 +21253,7 @@
         <v>732</v>
       </c>
       <c r="F881" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="882" spans="1:6" x14ac:dyDescent="0.35">
@@ -21151,7 +21292,7 @@
         <v>732</v>
       </c>
       <c r="F883" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="884" spans="1:6" x14ac:dyDescent="0.35">
@@ -21190,7 +21331,7 @@
         <v>733</v>
       </c>
       <c r="F885" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="886" spans="1:6" x14ac:dyDescent="0.35">
@@ -21211,7 +21352,7 @@
         <v>729</v>
       </c>
       <c r="F886" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="887" spans="1:6" x14ac:dyDescent="0.35">
@@ -21232,7 +21373,7 @@
         <v>733</v>
       </c>
       <c r="F887" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="888" spans="1:6" x14ac:dyDescent="0.35">
@@ -21253,7 +21394,7 @@
         <v>729</v>
       </c>
       <c r="F888" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="889" spans="1:6" x14ac:dyDescent="0.35">
@@ -21274,7 +21415,7 @@
         <v>733</v>
       </c>
       <c r="F889" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="890" spans="1:6" x14ac:dyDescent="0.35">
@@ -21295,7 +21436,7 @@
         <v>729</v>
       </c>
       <c r="F890" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="891" spans="1:6" x14ac:dyDescent="0.35">
@@ -21316,7 +21457,7 @@
         <v>733</v>
       </c>
       <c r="F891" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="892" spans="1:6" x14ac:dyDescent="0.35">
@@ -21337,7 +21478,7 @@
         <v>729</v>
       </c>
       <c r="F892" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="893" spans="1:6" x14ac:dyDescent="0.35">
@@ -21358,7 +21499,7 @@
         <v>733</v>
       </c>
       <c r="F893" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="894" spans="1:6" x14ac:dyDescent="0.35">
@@ -21396,7 +21537,7 @@
         <v>733</v>
       </c>
       <c r="F895" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="896" spans="1:6" x14ac:dyDescent="0.35">
@@ -21417,7 +21558,7 @@
         <v>729</v>
       </c>
       <c r="F896" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="897" spans="1:6" x14ac:dyDescent="0.35">
@@ -21438,7 +21579,7 @@
         <v>733</v>
       </c>
       <c r="F897" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.35">
@@ -21459,7 +21600,7 @@
         <v>729</v>
       </c>
       <c r="F898" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="899" spans="1:6" x14ac:dyDescent="0.35">
@@ -21480,7 +21621,7 @@
         <v>733</v>
       </c>
       <c r="F899" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="900" spans="1:6" x14ac:dyDescent="0.35">
@@ -21501,7 +21642,7 @@
         <v>729</v>
       </c>
       <c r="F900" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="901" spans="1:6" x14ac:dyDescent="0.35">
@@ -21522,7 +21663,7 @@
         <v>733</v>
       </c>
       <c r="F901" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="902" spans="1:6" x14ac:dyDescent="0.35">
@@ -21543,7 +21684,7 @@
         <v>729</v>
       </c>
       <c r="F902" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="903" spans="1:6" x14ac:dyDescent="0.35">
@@ -21564,7 +21705,7 @@
         <v>733</v>
       </c>
       <c r="F903" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="904" spans="1:6" x14ac:dyDescent="0.35">
@@ -21585,7 +21726,7 @@
         <v>729</v>
       </c>
       <c r="F904" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="905" spans="1:6" x14ac:dyDescent="0.35">
@@ -21606,7 +21747,7 @@
         <v>733</v>
       </c>
       <c r="F905" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="906" spans="1:6" x14ac:dyDescent="0.35">
@@ -21627,7 +21768,7 @@
         <v>729</v>
       </c>
       <c r="F906" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="907" spans="1:6" x14ac:dyDescent="0.35">
@@ -21648,7 +21789,7 @@
         <v>733</v>
       </c>
       <c r="F907" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="908" spans="1:6" x14ac:dyDescent="0.35">
@@ -21669,7 +21810,7 @@
         <v>729</v>
       </c>
       <c r="F908" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="909" spans="1:6" x14ac:dyDescent="0.35">
@@ -21690,7 +21831,7 @@
         <v>733</v>
       </c>
       <c r="F909" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.35">
@@ -21711,7 +21852,7 @@
         <v>729</v>
       </c>
       <c r="F910" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.35">
@@ -21732,7 +21873,7 @@
         <v>733</v>
       </c>
       <c r="F911" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="912" spans="1:6" x14ac:dyDescent="0.35">
@@ -21753,7 +21894,7 @@
         <v>729</v>
       </c>
       <c r="F912" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="913" spans="1:6" x14ac:dyDescent="0.35">
@@ -21774,7 +21915,7 @@
         <v>733</v>
       </c>
       <c r="F913" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.35">
@@ -21795,7 +21936,7 @@
         <v>729</v>
       </c>
       <c r="F914" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="915" spans="1:6" x14ac:dyDescent="0.35">
@@ -21816,7 +21957,7 @@
         <v>733</v>
       </c>
       <c r="F915" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="916" spans="1:6" x14ac:dyDescent="0.35">
@@ -21837,7 +21978,7 @@
         <v>729</v>
       </c>
       <c r="F916" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="917" spans="1:6" x14ac:dyDescent="0.35">
@@ -21858,7 +21999,7 @@
         <v>733</v>
       </c>
       <c r="F917" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="918" spans="1:6" x14ac:dyDescent="0.35">
@@ -21879,7 +22020,7 @@
         <v>729</v>
       </c>
       <c r="F918" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="919" spans="1:6" x14ac:dyDescent="0.35">
@@ -21900,7 +22041,7 @@
         <v>733</v>
       </c>
       <c r="F919" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="920" spans="1:6" x14ac:dyDescent="0.35">
@@ -21921,7 +22062,7 @@
         <v>729</v>
       </c>
       <c r="F920" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="921" spans="1:6" x14ac:dyDescent="0.35">
@@ -21942,7 +22083,7 @@
         <v>733</v>
       </c>
       <c r="F921" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="922" spans="1:6" x14ac:dyDescent="0.35">
@@ -21963,7 +22104,7 @@
         <v>729</v>
       </c>
       <c r="F922" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="923" spans="1:6" x14ac:dyDescent="0.35">
@@ -21984,7 +22125,7 @@
         <v>733</v>
       </c>
       <c r="F923" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="924" spans="1:6" x14ac:dyDescent="0.35">
@@ -22005,7 +22146,7 @@
         <v>729</v>
       </c>
       <c r="F924" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="925" spans="1:6" x14ac:dyDescent="0.35">
@@ -22026,7 +22167,7 @@
         <v>733</v>
       </c>
       <c r="F925" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="926" spans="1:6" x14ac:dyDescent="0.35">
@@ -22047,7 +22188,7 @@
         <v>729</v>
       </c>
       <c r="F926" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="927" spans="1:6" x14ac:dyDescent="0.35">
@@ -22068,7 +22209,7 @@
         <v>733</v>
       </c>
       <c r="F927" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="928" spans="1:6" x14ac:dyDescent="0.35">
@@ -22089,7 +22230,7 @@
         <v>729</v>
       </c>
       <c r="F928" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="929" spans="1:6" x14ac:dyDescent="0.35">
@@ -22110,7 +22251,7 @@
         <v>733</v>
       </c>
       <c r="F929" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="930" spans="1:6" x14ac:dyDescent="0.35">
@@ -22131,7 +22272,7 @@
         <v>729</v>
       </c>
       <c r="F930" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="931" spans="1:6" x14ac:dyDescent="0.35">
@@ -22152,7 +22293,7 @@
         <v>733</v>
       </c>
       <c r="F931" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="932" spans="1:6" x14ac:dyDescent="0.35">
@@ -22173,7 +22314,7 @@
         <v>729</v>
       </c>
       <c r="F932" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="933" spans="1:6" x14ac:dyDescent="0.35">
@@ -22212,7 +22353,7 @@
         <v>723</v>
       </c>
       <c r="F934" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="935" spans="1:6" x14ac:dyDescent="0.35">
@@ -22233,7 +22374,7 @@
         <v>723</v>
       </c>
       <c r="F935" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="936" spans="1:6" x14ac:dyDescent="0.35">
@@ -22254,7 +22395,7 @@
         <v>723</v>
       </c>
       <c r="F936" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="937" spans="1:6" x14ac:dyDescent="0.35">
@@ -22275,7 +22416,7 @@
         <v>723</v>
       </c>
       <c r="F937" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="938" spans="1:6" x14ac:dyDescent="0.35">
@@ -22296,7 +22437,7 @@
         <v>723</v>
       </c>
       <c r="F938" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="939" spans="1:6" x14ac:dyDescent="0.35">
@@ -22317,7 +22458,7 @@
         <v>730</v>
       </c>
       <c r="F939" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="940" spans="1:6" x14ac:dyDescent="0.35">
@@ -22390,7 +22531,7 @@
         <v>730</v>
       </c>
       <c r="F943" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="944" spans="1:6" x14ac:dyDescent="0.35">
@@ -22447,7 +22588,7 @@
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A947" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B947" t="s">
         <v>718</v>
@@ -22463,12 +22604,12 @@
         <v>730</v>
       </c>
       <c r="F947" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="948" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A948" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B948" t="s">
         <v>719</v>
@@ -22486,7 +22627,7 @@
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A949" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B949" t="s">
         <v>718</v>
@@ -22503,7 +22644,7 @@
     </row>
     <row r="950" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A950" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B950" t="s">
         <v>718</v>
@@ -22536,7 +22677,7 @@
         <v>723</v>
       </c>
       <c r="F951" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="952" spans="1:6" x14ac:dyDescent="0.35">
@@ -22557,7 +22698,7 @@
         <v>730</v>
       </c>
       <c r="F952" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.35">
@@ -22599,7 +22740,7 @@
         <v>723</v>
       </c>
       <c r="F954" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.35">
@@ -22620,7 +22761,7 @@
         <v>724</v>
       </c>
       <c r="F955" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.35">
@@ -22641,12 +22782,12 @@
         <v>721</v>
       </c>
       <c r="F956" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="957" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A957" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B957" t="s">
         <v>720</v>
@@ -22683,12 +22824,12 @@
         <v>723</v>
       </c>
       <c r="F958" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="959" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A959" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B959" t="s">
         <v>720</v>
@@ -22704,7 +22845,7 @@
         <v>723</v>
       </c>
       <c r="F959" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="960" spans="1:6" x14ac:dyDescent="0.35">
@@ -22725,7 +22866,7 @@
         <v>723</v>
       </c>
       <c r="F960" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="961" spans="1:6" x14ac:dyDescent="0.35">
@@ -22766,7 +22907,7 @@
     </row>
     <row r="963" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A963" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B963" t="s">
         <v>720</v>
@@ -22803,7 +22944,7 @@
         <v>723</v>
       </c>
       <c r="F964" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.35">
@@ -22860,7 +23001,7 @@
         <v>723</v>
       </c>
       <c r="F967" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="968" spans="1:6" x14ac:dyDescent="0.35">
@@ -22902,7 +23043,7 @@
         <v>723</v>
       </c>
       <c r="F969" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="970" spans="1:6" x14ac:dyDescent="0.35">
@@ -22923,7 +23064,7 @@
         <v>723</v>
       </c>
       <c r="F970" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="971" spans="1:6" x14ac:dyDescent="0.35">
@@ -22944,12 +23085,12 @@
         <v>723</v>
       </c>
       <c r="F971" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="972" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A972" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="B972" t="s">
         <v>720</v>
@@ -22965,7 +23106,7 @@
         <v>723</v>
       </c>
       <c r="F972" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="973" spans="1:6" x14ac:dyDescent="0.35">
@@ -22986,12 +23127,12 @@
         <v>723</v>
       </c>
       <c r="F973" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="974" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A974" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B974" t="s">
         <v>720</v>
@@ -23028,7 +23169,7 @@
         <v>721</v>
       </c>
       <c r="F975" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="976" spans="1:6" x14ac:dyDescent="0.35">
@@ -23049,7 +23190,7 @@
         <v>723</v>
       </c>
       <c r="F976" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="977" spans="1:6" x14ac:dyDescent="0.35">
@@ -23091,7 +23232,7 @@
         <v>724</v>
       </c>
       <c r="F978" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="979" spans="1:6" x14ac:dyDescent="0.35">
@@ -23112,7 +23253,7 @@
         <v>723</v>
       </c>
       <c r="F979" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="980" spans="1:6" x14ac:dyDescent="0.35">
@@ -23133,12 +23274,12 @@
         <v>723</v>
       </c>
       <c r="F980" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="981" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A981" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B981" t="s">
         <v>720</v>
@@ -23175,7 +23316,7 @@
         <v>721</v>
       </c>
       <c r="F982" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="983" spans="1:6" x14ac:dyDescent="0.35">
@@ -23196,12 +23337,12 @@
         <v>724</v>
       </c>
       <c r="F983" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="984" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A984" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B984" t="s">
         <v>720</v>
@@ -23217,7 +23358,7 @@
         <v>723</v>
       </c>
       <c r="F984" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="985" spans="1:6" x14ac:dyDescent="0.35">
@@ -23238,7 +23379,7 @@
         <v>723</v>
       </c>
       <c r="F985" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="986" spans="1:6" x14ac:dyDescent="0.35">
@@ -23259,7 +23400,7 @@
         <v>723</v>
       </c>
       <c r="F986" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="987" spans="1:6" x14ac:dyDescent="0.35">
@@ -23280,7 +23421,7 @@
         <v>723</v>
       </c>
       <c r="F987" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="988" spans="1:6" x14ac:dyDescent="0.35">
@@ -23400,7 +23541,7 @@
         <v>725</v>
       </c>
       <c r="F993" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="994" spans="1:6" x14ac:dyDescent="0.35">
@@ -23442,7 +23583,7 @@
         <v>725</v>
       </c>
       <c r="F995" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="996" spans="1:6" x14ac:dyDescent="0.35">
@@ -23484,7 +23625,7 @@
         <v>725</v>
       </c>
       <c r="F997" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="998" spans="1:6" x14ac:dyDescent="0.35">
@@ -23526,7 +23667,7 @@
         <v>725</v>
       </c>
       <c r="F999" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1000" spans="1:6" x14ac:dyDescent="0.35">
@@ -23568,7 +23709,7 @@
         <v>725</v>
       </c>
       <c r="F1001" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1002" spans="1:6" x14ac:dyDescent="0.35">
@@ -23610,7 +23751,7 @@
         <v>725</v>
       </c>
       <c r="F1003" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1004" spans="1:6" x14ac:dyDescent="0.35">
@@ -23652,7 +23793,7 @@
         <v>725</v>
       </c>
       <c r="F1005" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1006" spans="1:6" x14ac:dyDescent="0.35">
@@ -23694,7 +23835,7 @@
         <v>725</v>
       </c>
       <c r="F1007" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1008" spans="1:6" x14ac:dyDescent="0.35">
@@ -23736,7 +23877,7 @@
         <v>725</v>
       </c>
       <c r="F1009" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1010" spans="1:6" x14ac:dyDescent="0.35">
@@ -23778,7 +23919,7 @@
         <v>725</v>
       </c>
       <c r="F1011" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1012" spans="1:6" x14ac:dyDescent="0.35">
@@ -23820,7 +23961,7 @@
         <v>725</v>
       </c>
       <c r="F1013" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1014" spans="1:6" x14ac:dyDescent="0.35">
@@ -23862,7 +24003,7 @@
         <v>725</v>
       </c>
       <c r="F1015" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1016" spans="1:6" x14ac:dyDescent="0.35">
@@ -23904,7 +24045,7 @@
         <v>725</v>
       </c>
       <c r="F1017" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1018" spans="1:6" x14ac:dyDescent="0.35">
@@ -23946,7 +24087,7 @@
         <v>725</v>
       </c>
       <c r="F1019" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1020" spans="1:6" x14ac:dyDescent="0.35">
@@ -23988,7 +24129,7 @@
         <v>725</v>
       </c>
       <c r="F1021" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1022" spans="1:6" x14ac:dyDescent="0.35">
@@ -24030,7 +24171,7 @@
         <v>725</v>
       </c>
       <c r="F1023" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="1024" spans="1:6" x14ac:dyDescent="0.35">
@@ -24051,7 +24192,7 @@
         <v>730</v>
       </c>
       <c r="F1024" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="1025" spans="1:6" x14ac:dyDescent="0.35">
@@ -24090,7 +24231,7 @@
         <v>730</v>
       </c>
       <c r="F1026" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="1027" spans="1:6" x14ac:dyDescent="0.35">
@@ -24363,7 +24504,7 @@
         <v>730</v>
       </c>
       <c r="F1040" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="1041" spans="1:6" x14ac:dyDescent="0.35">
@@ -24402,7 +24543,7 @@
         <v>730</v>
       </c>
       <c r="F1042" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="1043" spans="1:6" x14ac:dyDescent="0.35">
@@ -24479,7 +24620,7 @@
         <v>730</v>
       </c>
       <c r="F1046" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="1047" spans="1:6" x14ac:dyDescent="0.35">
@@ -24500,7 +24641,7 @@
         <v>723</v>
       </c>
       <c r="F1047" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="1048" spans="1:6" x14ac:dyDescent="0.35">
@@ -24572,7 +24713,7 @@
         <v>730</v>
       </c>
       <c r="F1051" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="1052" spans="1:6" x14ac:dyDescent="0.35">
@@ -24649,7 +24790,7 @@
         <v>722</v>
       </c>
       <c r="F1055" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="1056" spans="1:6" x14ac:dyDescent="0.35">
@@ -24670,7 +24811,7 @@
         <v>730</v>
       </c>
       <c r="F1056" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="1057" spans="1:6" x14ac:dyDescent="0.35">
@@ -24863,7 +25004,7 @@
         <v>730</v>
       </c>
       <c r="F1066" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="1067" spans="1:6" x14ac:dyDescent="0.35">
@@ -24884,7 +25025,7 @@
         <v>723</v>
       </c>
       <c r="F1067" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="1068" spans="1:6" x14ac:dyDescent="0.35">
@@ -24998,7 +25139,7 @@
         <v>730</v>
       </c>
       <c r="F1073" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="1074" spans="1:6" x14ac:dyDescent="0.35">
@@ -25037,7 +25178,7 @@
         <v>730</v>
       </c>
       <c r="F1075" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="1076" spans="1:6" x14ac:dyDescent="0.35">
@@ -25076,7 +25217,7 @@
         <v>730</v>
       </c>
       <c r="F1077" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="1078" spans="1:6" x14ac:dyDescent="0.35">
@@ -25115,7 +25256,7 @@
         <v>730</v>
       </c>
       <c r="F1079" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="1080" spans="1:6" x14ac:dyDescent="0.35">
@@ -25192,7 +25333,7 @@
         <v>730</v>
       </c>
       <c r="F1083" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="1084" spans="1:6" x14ac:dyDescent="0.35">
@@ -25213,7 +25354,7 @@
         <v>723</v>
       </c>
       <c r="F1084" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="1085" spans="1:6" x14ac:dyDescent="0.35">
@@ -25306,7 +25447,7 @@
         <v>729</v>
       </c>
       <c r="F1089" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="1090" spans="1:6" x14ac:dyDescent="0.35">
@@ -25348,7 +25489,7 @@
         <v>729</v>
       </c>
       <c r="F1091" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="1092" spans="1:6" x14ac:dyDescent="0.35">
@@ -25516,7 +25657,7 @@
         <v>723</v>
       </c>
       <c r="F1099" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="1100" spans="1:6" x14ac:dyDescent="0.35">
@@ -25558,7 +25699,7 @@
         <v>723</v>
       </c>
       <c r="F1101" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="1102" spans="1:6" x14ac:dyDescent="0.35">
@@ -25579,7 +25720,7 @@
         <v>730</v>
       </c>
       <c r="F1102" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1103" spans="1:6" x14ac:dyDescent="0.35">
@@ -25621,7 +25762,7 @@
         <v>730</v>
       </c>
       <c r="F1104" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="1105" spans="1:6" x14ac:dyDescent="0.35">
@@ -25663,7 +25804,7 @@
         <v>730</v>
       </c>
       <c r="F1106" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="1107" spans="1:6" x14ac:dyDescent="0.35">
@@ -25678,7 +25819,7 @@
         <v>7.7419354838709681E-2</v>
       </c>
       <c r="D1107" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E1107" t="s">
         <v>723</v>
@@ -25726,7 +25867,7 @@
         <v>730</v>
       </c>
       <c r="F1109" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="1110" spans="1:6" x14ac:dyDescent="0.35">
@@ -25789,7 +25930,7 @@
         <v>730</v>
       </c>
       <c r="F1112" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="1113" spans="1:6" x14ac:dyDescent="0.35">
@@ -25852,7 +25993,7 @@
         <v>730</v>
       </c>
       <c r="F1115" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="1116" spans="1:6" x14ac:dyDescent="0.35">
@@ -25867,7 +26008,7 @@
         <v>7.7419354838709681E-2</v>
       </c>
       <c r="D1116" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E1116" t="s">
         <v>723</v>
@@ -25894,7 +26035,7 @@
         <v>730</v>
       </c>
       <c r="F1117" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="1118" spans="1:6" x14ac:dyDescent="0.35">
@@ -25936,7 +26077,7 @@
         <v>730</v>
       </c>
       <c r="F1119" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="1120" spans="1:6" x14ac:dyDescent="0.35">
@@ -26058,7 +26199,7 @@
         <v>723</v>
       </c>
       <c r="F1125" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="1126" spans="1:6" x14ac:dyDescent="0.35">
@@ -26079,7 +26220,7 @@
         <v>730</v>
       </c>
       <c r="F1126" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="1127" spans="1:6" x14ac:dyDescent="0.35">
@@ -26100,7 +26241,7 @@
         <v>723</v>
       </c>
       <c r="F1127" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="1128" spans="1:6" x14ac:dyDescent="0.35">
@@ -26121,7 +26262,7 @@
         <v>730</v>
       </c>
       <c r="F1128" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="1129" spans="1:6" x14ac:dyDescent="0.35">
@@ -26142,7 +26283,7 @@
         <v>723</v>
       </c>
       <c r="F1129" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="1130" spans="1:6" x14ac:dyDescent="0.35">
@@ -26319,7 +26460,7 @@
         <v>733</v>
       </c>
       <c r="F1138" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="1139" spans="1:6" x14ac:dyDescent="0.35">
@@ -26340,7 +26481,7 @@
         <v>729</v>
       </c>
       <c r="F1139" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="1140" spans="1:6" x14ac:dyDescent="0.35">
@@ -26361,7 +26502,7 @@
         <v>733</v>
       </c>
       <c r="F1140" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="1141" spans="1:6" x14ac:dyDescent="0.35">
@@ -26382,7 +26523,7 @@
         <v>729</v>
       </c>
       <c r="F1141" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="1142" spans="1:6" x14ac:dyDescent="0.35">
@@ -26424,7 +26565,7 @@
         <v>729</v>
       </c>
       <c r="F1143" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="1144" spans="1:6" x14ac:dyDescent="0.35">
@@ -26456,14 +26597,17 @@
         <v>719</v>
       </c>
       <c r="C1145">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1145" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1145" t="s">
         <v>725</v>
+      </c>
+      <c r="F1145" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1146" spans="1:6" x14ac:dyDescent="0.35">
@@ -26495,14 +26639,17 @@
         <v>719</v>
       </c>
       <c r="C1147">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1147" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1147" t="s">
         <v>725</v>
+      </c>
+      <c r="F1147" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1148" spans="1:6" x14ac:dyDescent="0.35">
@@ -26534,14 +26681,17 @@
         <v>719</v>
       </c>
       <c r="C1149">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1149" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1149" t="s">
         <v>725</v>
+      </c>
+      <c r="F1149" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1150" spans="1:6" x14ac:dyDescent="0.35">
@@ -26573,14 +26723,17 @@
         <v>719</v>
       </c>
       <c r="C1151">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1151" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1151" t="s">
         <v>725</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1152" spans="1:6" x14ac:dyDescent="0.35">
@@ -26612,14 +26765,17 @@
         <v>719</v>
       </c>
       <c r="C1153">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1153" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1153" t="s">
         <v>725</v>
+      </c>
+      <c r="F1153" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1154" spans="1:6" x14ac:dyDescent="0.35">
@@ -26651,14 +26807,17 @@
         <v>719</v>
       </c>
       <c r="C1155">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1155" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1155" t="s">
         <v>725</v>
+      </c>
+      <c r="F1155" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1156" spans="1:6" x14ac:dyDescent="0.35">
@@ -26690,14 +26849,17 @@
         <v>719</v>
       </c>
       <c r="C1157">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1157" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1157" t="s">
         <v>725</v>
+      </c>
+      <c r="F1157" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1158" spans="1:6" x14ac:dyDescent="0.35">
@@ -26729,14 +26891,17 @@
         <v>719</v>
       </c>
       <c r="C1159">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1159" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1159" t="s">
         <v>725</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1160" spans="1:6" x14ac:dyDescent="0.35">
@@ -26768,14 +26933,17 @@
         <v>719</v>
       </c>
       <c r="C1161">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1161" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1161" t="s">
         <v>725</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1162" spans="1:6" x14ac:dyDescent="0.35">
@@ -26807,14 +26975,17 @@
         <v>719</v>
       </c>
       <c r="C1163">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1163" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1163" t="s">
         <v>725</v>
+      </c>
+      <c r="F1163" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1164" spans="1:6" x14ac:dyDescent="0.35">
@@ -26846,14 +27017,17 @@
         <v>719</v>
       </c>
       <c r="C1165">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1165" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1165" t="s">
         <v>725</v>
+      </c>
+      <c r="F1165" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1166" spans="1:6" x14ac:dyDescent="0.35">
@@ -26885,14 +27059,17 @@
         <v>719</v>
       </c>
       <c r="C1167">
-        <f>1</f>
-        <v>1</v>
+        <f>1/1.23</f>
+        <v>0.81300813008130079</v>
       </c>
       <c r="D1167" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E1167" t="s">
         <v>725</v>
+      </c>
+      <c r="F1167" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="1168" spans="1:6" x14ac:dyDescent="0.35">
@@ -26913,7 +27090,7 @@
         <v>732</v>
       </c>
       <c r="F1168" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="1169" spans="1:6" x14ac:dyDescent="0.35">
@@ -26952,7 +27129,7 @@
         <v>732</v>
       </c>
       <c r="F1170" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="1171" spans="1:6" x14ac:dyDescent="0.35">
@@ -26991,7 +27168,7 @@
         <v>733</v>
       </c>
       <c r="F1172" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="1173" spans="1:6" x14ac:dyDescent="0.35">
@@ -27028,7 +27205,7 @@
         <v>722</v>
       </c>
       <c r="F1174" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="1175" spans="1:6" x14ac:dyDescent="0.35">
@@ -27048,7 +27225,7 @@
         <v>722</v>
       </c>
       <c r="F1175" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="1176" spans="1:6" x14ac:dyDescent="0.35">
@@ -27069,7 +27246,7 @@
         <v>733</v>
       </c>
       <c r="F1176" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="1177" spans="1:6" x14ac:dyDescent="0.35">
@@ -27106,7 +27283,7 @@
         <v>722</v>
       </c>
       <c r="F1178" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="1179" spans="1:6" x14ac:dyDescent="0.35">
@@ -27126,7 +27303,7 @@
         <v>722</v>
       </c>
       <c r="F1179" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="1180" spans="1:6" x14ac:dyDescent="0.35">
@@ -27147,7 +27324,7 @@
         <v>733</v>
       </c>
       <c r="F1180" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="1181" spans="1:6" x14ac:dyDescent="0.35">
@@ -27184,7 +27361,7 @@
         <v>722</v>
       </c>
       <c r="F1182" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="1183" spans="1:6" x14ac:dyDescent="0.35">
@@ -27204,7 +27381,7 @@
         <v>722</v>
       </c>
       <c r="F1183" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="1184" spans="1:6" x14ac:dyDescent="0.35">
@@ -27225,7 +27402,7 @@
         <v>733</v>
       </c>
       <c r="F1184" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="1185" spans="1:6" x14ac:dyDescent="0.35">
@@ -27262,7 +27439,7 @@
         <v>722</v>
       </c>
       <c r="F1186" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="1187" spans="1:6" x14ac:dyDescent="0.35">
@@ -27282,7 +27459,7 @@
         <v>722</v>
       </c>
       <c r="F1187" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="1188" spans="1:6" x14ac:dyDescent="0.35">
@@ -27303,7 +27480,7 @@
         <v>732</v>
       </c>
       <c r="F1188" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="1189" spans="1:6" x14ac:dyDescent="0.35">
@@ -27342,7 +27519,7 @@
         <v>732</v>
       </c>
       <c r="F1190" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="1191" spans="1:6" x14ac:dyDescent="0.35">
@@ -27381,7 +27558,7 @@
         <v>733</v>
       </c>
       <c r="F1192" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="1193" spans="1:6" x14ac:dyDescent="0.35">
@@ -27402,7 +27579,7 @@
         <v>729</v>
       </c>
       <c r="F1193" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="1194" spans="1:6" x14ac:dyDescent="0.35">
@@ -27423,7 +27600,7 @@
         <v>733</v>
       </c>
       <c r="F1194" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="1195" spans="1:6" x14ac:dyDescent="0.35">
@@ -27444,7 +27621,7 @@
         <v>729</v>
       </c>
       <c r="F1195" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1196" spans="1:6" x14ac:dyDescent="0.35">
@@ -27465,7 +27642,7 @@
         <v>733</v>
       </c>
       <c r="F1196" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="1197" spans="1:6" x14ac:dyDescent="0.35">
@@ -27486,7 +27663,7 @@
         <v>729</v>
       </c>
       <c r="F1197" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1198" spans="1:6" x14ac:dyDescent="0.35">
@@ -27512,7 +27689,7 @@
     </row>
     <row r="1199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1199" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B1199" t="s">
         <v>718</v>
@@ -27528,12 +27705,12 @@
         <v>730</v>
       </c>
       <c r="F1199" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="1200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1200" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B1200" t="s">
         <v>718</v>
@@ -27549,12 +27726,12 @@
         <v>730</v>
       </c>
       <c r="F1200" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="1201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1201" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B1201" t="s">
         <v>718</v>
@@ -27570,12 +27747,12 @@
         <v>730</v>
       </c>
       <c r="F1201" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="1202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1202" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B1202" t="s">
         <v>718</v>
@@ -27591,12 +27768,12 @@
         <v>730</v>
       </c>
       <c r="F1202" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="1203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1203" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B1203" t="s">
         <v>718</v>
@@ -27612,12 +27789,12 @@
         <v>730</v>
       </c>
       <c r="F1203" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="1204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1204" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B1204" t="s">
         <v>718</v>
@@ -27633,12 +27810,12 @@
         <v>730</v>
       </c>
       <c r="F1204" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="1205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1205" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B1205" t="s">
         <v>718</v>
@@ -27654,12 +27831,12 @@
         <v>730</v>
       </c>
       <c r="F1205" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="1206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1206" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B1206" t="s">
         <v>718</v>
@@ -27675,7 +27852,7 @@
         <v>730</v>
       </c>
       <c r="F1206" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="1207" spans="1:6" x14ac:dyDescent="0.35">
@@ -27683,7 +27860,7 @@
         <v>6</v>
       </c>
       <c r="B1207" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1207">
         <f>1 * 3.6 / 14.55</f>
@@ -27704,7 +27881,7 @@
         <v>7</v>
       </c>
       <c r="B1208" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1208">
         <f>1 / 8.22</f>
@@ -27725,7 +27902,7 @@
         <v>27</v>
       </c>
       <c r="B1209" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1209">
         <f>1 * 3.6 / 42.5</f>
@@ -27746,7 +27923,7 @@
         <v>53</v>
       </c>
       <c r="B1210" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1210">
         <f>1 / 10.5</f>
@@ -27767,7 +27944,7 @@
         <v>150</v>
       </c>
       <c r="B1211" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1211">
         <f>1 * 3.6 / 27.91</f>
@@ -27788,7 +27965,7 @@
         <v>227</v>
       </c>
       <c r="B1212" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1212">
         <f>1 / 11.83</f>
@@ -27809,7 +27986,7 @@
         <v>232</v>
       </c>
       <c r="B1213" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1213">
         <f>1</f>
@@ -27824,10 +28001,10 @@
     </row>
     <row r="1214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1214" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B1214" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1214">
         <f>1</f>
@@ -27842,10 +28019,10 @@
     </row>
     <row r="1215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1215" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B1215" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1215">
         <f>1</f>
@@ -27860,10 +28037,10 @@
     </row>
     <row r="1216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1216" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B1216" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1216">
         <f>1</f>
@@ -27881,7 +28058,7 @@
         <v>236</v>
       </c>
       <c r="B1217" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1217">
         <f>1 / 13.28</f>
@@ -27902,7 +28079,7 @@
         <v>240</v>
       </c>
       <c r="B1218" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1218">
         <f>1 * 3.6 / 31.58</f>
@@ -27923,7 +28100,7 @@
         <v>242</v>
       </c>
       <c r="B1219" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1219">
         <f>1 * 3.6 / 40.938</f>
@@ -27944,7 +28121,7 @@
         <v>243</v>
       </c>
       <c r="B1220" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1220">
         <f>1 * 3.6 / 50.285</f>
@@ -27965,7 +28142,7 @@
         <v>255</v>
       </c>
       <c r="B1221" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1221">
         <f>1 * 3.6 / 42.5</f>
@@ -27986,7 +28163,7 @@
         <v>262</v>
       </c>
       <c r="B1222" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1222">
         <f>1 / 33.3</f>
@@ -28007,7 +28184,7 @@
         <v>269</v>
       </c>
       <c r="B1223" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1223">
         <f>1 / 33.3</f>
@@ -28028,7 +28205,7 @@
         <v>270</v>
       </c>
       <c r="B1224" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1224">
         <f>1 / 33.3</f>
@@ -28049,7 +28226,7 @@
         <v>271</v>
       </c>
       <c r="B1225" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1225">
         <f>1 / 33.3</f>
@@ -28070,7 +28247,7 @@
         <v>307</v>
       </c>
       <c r="B1226" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1226">
         <f>1 * 3.6 / 43</f>
@@ -28091,7 +28268,7 @@
         <v>326</v>
       </c>
       <c r="B1227" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1227">
         <f>1 * 3.6 / 42.6</f>
@@ -28112,7 +28289,7 @@
         <v>327</v>
       </c>
       <c r="B1228" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1228">
         <f>1 * 3.6 / 39</f>
@@ -28133,7 +28310,7 @@
         <v>332</v>
       </c>
       <c r="B1229" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1229">
         <f>1 / 5.54</f>
@@ -28154,7 +28331,7 @@
         <v>344</v>
       </c>
       <c r="B1230" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1230">
         <f>1 * 3.6 / 39</f>
@@ -28175,11 +28352,11 @@
         <v>351</v>
       </c>
       <c r="B1231" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1231">
-        <f>1 / (0.777 * 13.1)</f>
-        <v>9.8244373053533368E-2</v>
+        <f t="shared" ref="C1231:C1232" si="0">1 * 3.6 / 39</f>
+        <v>9.2307692307692313E-2</v>
       </c>
       <c r="D1231" t="s">
         <v>724</v>
@@ -28196,11 +28373,11 @@
         <v>352</v>
       </c>
       <c r="B1232" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1232">
-        <f>1 / (0.777 * 13.1)</f>
-        <v>9.8244373053533368E-2</v>
+        <f t="shared" si="0"/>
+        <v>9.2307692307692313E-2</v>
       </c>
       <c r="D1232" t="s">
         <v>724</v>
@@ -28217,20 +28394,20 @@
         <v>353</v>
       </c>
       <c r="B1233" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1233">
-        <f>1 / (0.777 * 13.1)</f>
-        <v>9.8244373053533368E-2</v>
+        <f>1 * 3.6 / 46.5</f>
+        <v>7.7419354838709681E-2</v>
       </c>
       <c r="D1233" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E1233" t="s">
         <v>723</v>
       </c>
       <c r="F1233" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="1234" spans="1:6" x14ac:dyDescent="0.35">
@@ -28238,7 +28415,7 @@
         <v>367</v>
       </c>
       <c r="B1234" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1234">
         <f>1</f>
@@ -28256,7 +28433,7 @@
         <v>374</v>
       </c>
       <c r="B1235" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1235">
         <f>1</f>
@@ -28274,7 +28451,7 @@
         <v>376</v>
       </c>
       <c r="B1236" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1236">
         <f>1 * 3.6 / 32.45</f>
@@ -28295,7 +28472,7 @@
         <v>381</v>
       </c>
       <c r="B1237" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1237">
         <f>1</f>
@@ -28313,7 +28490,7 @@
         <v>382</v>
       </c>
       <c r="B1238" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1238">
         <f>1 * 3.6 / 46.4</f>
@@ -28334,7 +28511,7 @@
         <v>383</v>
       </c>
       <c r="B1239" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1239">
         <f>1 * 3.6 / 45.799</f>
@@ -28355,7 +28532,7 @@
         <v>384</v>
       </c>
       <c r="B1240" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1240">
         <f>1</f>
@@ -28373,7 +28550,7 @@
         <v>385</v>
       </c>
       <c r="B1241" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1241">
         <f>1</f>
@@ -28388,53 +28565,53 @@
     </row>
     <row r="1242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1242" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="B1242" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1242">
-        <f>1 / (0.777 * 13.1)</f>
-        <v>9.8244373053533368E-2</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="D1242" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E1242" t="s">
-        <v>723</v>
-      </c>
-      <c r="F1242" t="s">
-        <v>808</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1243" t="s">
-        <v>439</v>
+        <v>490</v>
       </c>
       <c r="B1243" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1243">
-        <f>1</f>
-        <v>1</v>
+        <f>1 * 3.6 / 42.43</f>
+        <v>8.4845628093330197E-2</v>
       </c>
       <c r="D1243" t="s">
         <v>721</v>
       </c>
       <c r="E1243" t="s">
-        <v>721</v>
+        <v>723</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="1244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1244" t="s">
-        <v>490</v>
+        <v>561</v>
       </c>
       <c r="B1244" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1244">
-        <f>1 * 3.6 / 42.43</f>
-        <v>8.4845628093330197E-2</v>
+        <f>1 * 3.6 / (3900*1000)</f>
+        <v>9.2307692307692312E-7</v>
       </c>
       <c r="D1244" t="s">
         <v>721</v>
@@ -28443,19 +28620,19 @@
         <v>723</v>
       </c>
       <c r="F1244" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="1245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1245" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B1245" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1245">
-        <f>1 * 3.6 / (3900*1000)</f>
-        <v>9.2307692307692312E-7</v>
+        <f>-1 * 3.6 / 12.35</f>
+        <v>-0.29149797570850206</v>
       </c>
       <c r="D1245" t="s">
         <v>721</v>
@@ -28469,14 +28646,14 @@
     </row>
     <row r="1246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1246" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B1246" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1246">
-        <f>-1 * 3.6 / 12.35</f>
-        <v>-0.29149797570850206</v>
+        <f>-1 * 3.6 / (6.087*0.95)</f>
+        <v>-0.62255194417784243</v>
       </c>
       <c r="D1246" t="s">
         <v>721</v>
@@ -28490,14 +28667,14 @@
     </row>
     <row r="1247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1247" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B1247" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1247">
-        <f>-1 * 3.6 / (6.087*0.95)</f>
-        <v>-0.62255194417784243</v>
+        <f>-1 * 3.6 / 2.453</f>
+        <v>-1.4675907052588668</v>
       </c>
       <c r="D1247" t="s">
         <v>721</v>
@@ -28511,14 +28688,14 @@
     </row>
     <row r="1248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1248" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B1248" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1248">
-        <f>-1 * 3.6 / 2.453</f>
-        <v>-1.4675907052588668</v>
+        <f>1 * 3.6 / (0.95*15)</f>
+        <v>0.25263157894736843</v>
       </c>
       <c r="D1248" t="s">
         <v>721</v>
@@ -28527,19 +28704,19 @@
         <v>723</v>
       </c>
       <c r="F1248" t="s">
-        <v>817</v>
+        <v>828</v>
       </c>
     </row>
     <row r="1249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1249" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B1249" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1249">
-        <f>1 * 3.6 / (0.95*15)</f>
-        <v>0.25263157894736843</v>
+        <f>1 * 3.6 / 15.4</f>
+        <v>0.23376623376623376</v>
       </c>
       <c r="D1249" t="s">
         <v>721</v>
@@ -28548,19 +28725,19 @@
         <v>723</v>
       </c>
       <c r="F1249" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
     </row>
     <row r="1250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1250" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B1250" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1250">
-        <f>1 * 3.6 / 15.4</f>
-        <v>0.23376623376623376</v>
+        <f>1 * 3.6 / 40.961</f>
+        <v>8.788847928517371E-2</v>
       </c>
       <c r="D1250" t="s">
         <v>721</v>
@@ -28569,19 +28746,19 @@
         <v>723</v>
       </c>
       <c r="F1250" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="1251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1251" t="s">
-        <v>574</v>
+        <v>716</v>
       </c>
       <c r="B1251" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1251">
-        <f>1 * 3.6 / 40.961</f>
-        <v>8.788847928517371E-2</v>
+        <f>1 * 3.6 / 31.58</f>
+        <v>0.11399620012666245</v>
       </c>
       <c r="D1251" t="s">
         <v>721</v>
@@ -28590,19 +28767,19 @@
         <v>723</v>
       </c>
       <c r="F1251" t="s">
-        <v>820</v>
+        <v>766</v>
       </c>
     </row>
     <row r="1252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1252" t="s">
-        <v>716</v>
+        <v>846</v>
       </c>
       <c r="B1252" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1252">
-        <f>1 * 3.6 / 31.58</f>
-        <v>0.11399620012666245</v>
+        <f>1 * 3.6 / 43</f>
+        <v>8.3720930232558138E-2</v>
       </c>
       <c r="D1252" t="s">
         <v>721</v>
@@ -28611,7 +28788,7 @@
         <v>723</v>
       </c>
       <c r="F1252" t="s">
-        <v>766</v>
+        <v>782</v>
       </c>
     </row>
     <row r="1253" spans="1:6" x14ac:dyDescent="0.35">
@@ -28619,11 +28796,11 @@
         <v>847</v>
       </c>
       <c r="B1253" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1253">
-        <f>1 * 3.6 / 43</f>
-        <v>8.3720930232558138E-2</v>
+        <f>1 * 3.6 / 42.6</f>
+        <v>8.4507042253521125E-2</v>
       </c>
       <c r="D1253" t="s">
         <v>721</v>
@@ -28632,7 +28809,7 @@
         <v>723</v>
       </c>
       <c r="F1253" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="1254" spans="1:6" x14ac:dyDescent="0.35">
@@ -28640,11 +28817,11 @@
         <v>848</v>
       </c>
       <c r="B1254" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1254">
-        <f>1 * 3.6 / 42.6</f>
-        <v>8.4507042253521125E-2</v>
+        <f>1 / 5.54</f>
+        <v>0.18050541516245489</v>
       </c>
       <c r="D1254" t="s">
         <v>721</v>
@@ -28653,40 +28830,40 @@
         <v>723</v>
       </c>
       <c r="F1254" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
     </row>
     <row r="1255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1255" t="s">
-        <v>849</v>
+        <v>428</v>
       </c>
       <c r="B1255" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1255">
-        <f>1 / 5.54</f>
-        <v>0.18050541516245489</v>
+        <f>1 * 3.6 / 39</f>
+        <v>9.2307692307692313E-2</v>
       </c>
       <c r="D1255" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="E1255" t="s">
         <v>723</v>
       </c>
       <c r="F1255" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="1256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1256" t="s">
-        <v>428</v>
+        <v>849</v>
       </c>
       <c r="B1256" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1256">
-        <f>1 * 3.6 / 39</f>
-        <v>9.2307692307692313E-2</v>
+        <f>1 / (0.777 * 13.1)</f>
+        <v>9.8244373053533368E-2</v>
       </c>
       <c r="D1256" t="s">
         <v>724</v>
@@ -28700,10 +28877,10 @@
     </row>
     <row r="1257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1257" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B1257" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1257">
         <f>1 / (0.777 * 13.1)</f>
@@ -28721,10 +28898,10 @@
     </row>
     <row r="1258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1258" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B1258" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1258">
         <f>1 / (0.777 * 13.1)</f>
@@ -28742,31 +28919,28 @@
     </row>
     <row r="1259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1259" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="B1259" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1259">
-        <f>1 / (0.777 * 13.1)</f>
-        <v>9.8244373053533368E-2</v>
+        <f>1 * 3.6</f>
+        <v>3.6</v>
       </c>
       <c r="D1259" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="E1259" t="s">
         <v>723</v>
-      </c>
-      <c r="F1259" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="1260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1260" t="s">
-        <v>856</v>
+        <v>1022</v>
       </c>
       <c r="B1260" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1260">
         <f>1 * 3.6</f>
@@ -28781,20 +28955,19 @@
     </row>
     <row r="1261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1261" t="s">
-        <v>1023</v>
+        <v>856</v>
       </c>
       <c r="B1261" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1261">
-        <f>1 * 3.6</f>
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="D1261" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="E1261" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1262" spans="1:6" x14ac:dyDescent="0.35">
@@ -28802,7 +28975,7 @@
         <v>857</v>
       </c>
       <c r="B1262" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1262">
         <v>1</v>
@@ -28816,10 +28989,10 @@
     </row>
     <row r="1263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1263" t="s">
-        <v>858</v>
+        <v>1023</v>
       </c>
       <c r="B1263" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1263">
         <v>1</v>
@@ -28833,19 +29006,23 @@
     </row>
     <row r="1264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1264" t="s">
-        <v>1024</v>
+        <v>864</v>
       </c>
       <c r="B1264" t="s">
-        <v>846</v>
+        <v>717</v>
       </c>
       <c r="C1264">
-        <v>1</v>
+        <f>3.6/18.43</f>
+        <v>0.19533369506239828</v>
       </c>
       <c r="D1264" t="s">
         <v>721</v>
       </c>
       <c r="E1264" t="s">
-        <v>721</v>
+        <v>723</v>
+      </c>
+      <c r="F1264" t="s">
+        <v>1005</v>
       </c>
     </row>
     <row r="1265" spans="1:6" x14ac:dyDescent="0.35">
@@ -28856,8 +29033,8 @@
         <v>717</v>
       </c>
       <c r="C1265">
-        <f>3.6/18.43</f>
-        <v>0.19533369506239828</v>
+        <f>3.6/18.61</f>
+        <v>0.19344438473938744</v>
       </c>
       <c r="D1265" t="s">
         <v>721</v>
@@ -28877,8 +29054,8 @@
         <v>717</v>
       </c>
       <c r="C1266">
-        <f>3.6/18.61</f>
-        <v>0.19344438473938744</v>
+        <f>3.6/19.06</f>
+        <v>0.1888772298006296</v>
       </c>
       <c r="D1266" t="s">
         <v>721</v>
@@ -28898,8 +29075,8 @@
         <v>717</v>
       </c>
       <c r="C1267">
-        <f>3.6/19.06</f>
-        <v>0.1888772298006296</v>
+        <f>3.6/18.93</f>
+        <v>0.19017432646592711</v>
       </c>
       <c r="D1267" t="s">
         <v>721</v>
@@ -28919,8 +29096,8 @@
         <v>717</v>
       </c>
       <c r="C1268">
-        <f>3.6/18.93</f>
-        <v>0.19017432646592711</v>
+        <f>3.6 / 7.09</f>
+        <v>0.50775740479548659</v>
       </c>
       <c r="D1268" t="s">
         <v>721</v>
@@ -28940,8 +29117,8 @@
         <v>717</v>
       </c>
       <c r="C1269">
-        <f>3.6 / 7.09</f>
-        <v>0.50775740479548659</v>
+        <f>3.6/15.34</f>
+        <v>0.23468057366362452</v>
       </c>
       <c r="D1269" t="s">
         <v>721</v>
@@ -28961,8 +29138,8 @@
         <v>717</v>
       </c>
       <c r="C1270">
-        <f>3.6/15.34</f>
-        <v>0.23468057366362452</v>
+        <f>-1 * 3.6 / 17.09</f>
+        <v>-0.2106495026331188</v>
       </c>
       <c r="D1270" t="s">
         <v>721</v>
@@ -28982,8 +29159,8 @@
         <v>717</v>
       </c>
       <c r="C1271">
-        <f>-1 * 3.6 / 17.09</f>
-        <v>-0.2106495026331188</v>
+        <f>3.6/15.98</f>
+        <v>0.22528160200250313</v>
       </c>
       <c r="D1271" t="s">
         <v>721</v>
@@ -29003,8 +29180,8 @@
         <v>717</v>
       </c>
       <c r="C1272">
-        <f>3.6/15.98</f>
-        <v>0.22528160200250313</v>
+        <f>-1 * 3.6 / 11.24</f>
+        <v>-0.32028469750889682</v>
       </c>
       <c r="D1272" t="s">
         <v>721</v>
@@ -29013,7 +29190,7 @@
         <v>723</v>
       </c>
       <c r="F1272" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="1273" spans="1:6" x14ac:dyDescent="0.35">
@@ -29024,8 +29201,8 @@
         <v>717</v>
       </c>
       <c r="C1273">
-        <f>-1 * 3.6 / 11.24</f>
-        <v>-0.32028469750889682</v>
+        <f>3.6/18.63</f>
+        <v>0.19323671497584544</v>
       </c>
       <c r="D1273" t="s">
         <v>721</v>
@@ -29034,7 +29211,7 @@
         <v>723</v>
       </c>
       <c r="F1273" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="1274" spans="1:6" x14ac:dyDescent="0.35">
@@ -29045,8 +29222,8 @@
         <v>717</v>
       </c>
       <c r="C1274">
-        <f>3.6/18.63</f>
-        <v>0.19323671497584544</v>
+        <f>-1 * 3.6 / 7.64</f>
+        <v>-0.47120418848167545</v>
       </c>
       <c r="D1274" t="s">
         <v>721</v>
@@ -29055,19 +29232,19 @@
         <v>723</v>
       </c>
       <c r="F1274" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="1275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1275" t="s">
-        <v>875</v>
+        <v>864</v>
       </c>
       <c r="B1275" t="s">
-        <v>717</v>
+        <v>845</v>
       </c>
       <c r="C1275">
-        <f>-1 * 3.6 / 7.64</f>
-        <v>-0.47120418848167545</v>
+        <f>3.6/18.43</f>
+        <v>0.19533369506239828</v>
       </c>
       <c r="D1275" t="s">
         <v>721</v>
@@ -29076,7 +29253,7 @@
         <v>723</v>
       </c>
       <c r="F1275" t="s">
-        <v>1016</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1276" spans="1:6" x14ac:dyDescent="0.35">
@@ -29084,11 +29261,11 @@
         <v>865</v>
       </c>
       <c r="B1276" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1276">
-        <f>3.6/18.43</f>
-        <v>0.19533369506239828</v>
+        <f>3.6/18.61</f>
+        <v>0.19344438473938744</v>
       </c>
       <c r="D1276" t="s">
         <v>721</v>
@@ -29105,11 +29282,11 @@
         <v>866</v>
       </c>
       <c r="B1277" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1277">
-        <f>3.6/18.61</f>
-        <v>0.19344438473938744</v>
+        <f>3.6/19.06</f>
+        <v>0.1888772298006296</v>
       </c>
       <c r="D1277" t="s">
         <v>721</v>
@@ -29126,11 +29303,11 @@
         <v>867</v>
       </c>
       <c r="B1278" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1278">
-        <f>3.6/19.06</f>
-        <v>0.1888772298006296</v>
+        <f>3.6/18.93</f>
+        <v>0.19017432646592711</v>
       </c>
       <c r="D1278" t="s">
         <v>721</v>
@@ -29147,11 +29324,11 @@
         <v>868</v>
       </c>
       <c r="B1279" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1279">
-        <f>3.6/18.93</f>
-        <v>0.19017432646592711</v>
+        <f>3.6 / 7.09</f>
+        <v>0.50775740479548659</v>
       </c>
       <c r="D1279" t="s">
         <v>721</v>
@@ -29168,11 +29345,11 @@
         <v>869</v>
       </c>
       <c r="B1280" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1280">
-        <f>3.6 / 7.09</f>
-        <v>0.50775740479548659</v>
+        <f>3.6/15.34</f>
+        <v>0.23468057366362452</v>
       </c>
       <c r="D1280" t="s">
         <v>721</v>
@@ -29189,11 +29366,11 @@
         <v>870</v>
       </c>
       <c r="B1281" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1281">
-        <f>3.6/15.34</f>
-        <v>0.23468057366362452</v>
+        <f>-1 * 3.6 / 17.09</f>
+        <v>-0.2106495026331188</v>
       </c>
       <c r="D1281" t="s">
         <v>721</v>
@@ -29210,11 +29387,11 @@
         <v>871</v>
       </c>
       <c r="B1282" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1282">
-        <f>-1 * 3.6 / 17.09</f>
-        <v>-0.2106495026331188</v>
+        <f>3.6/15.98</f>
+        <v>0.22528160200250313</v>
       </c>
       <c r="D1282" t="s">
         <v>721</v>
@@ -29231,11 +29408,11 @@
         <v>872</v>
       </c>
       <c r="B1283" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1283">
-        <f>3.6/15.98</f>
-        <v>0.22528160200250313</v>
+        <f>-1 * 3.6 / 11.24</f>
+        <v>-0.32028469750889682</v>
       </c>
       <c r="D1283" t="s">
         <v>721</v>
@@ -29244,7 +29421,7 @@
         <v>723</v>
       </c>
       <c r="F1283" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="1284" spans="1:6" x14ac:dyDescent="0.35">
@@ -29252,11 +29429,11 @@
         <v>873</v>
       </c>
       <c r="B1284" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1284">
-        <f>-1 * 3.6 / 11.24</f>
-        <v>-0.32028469750889682</v>
+        <f>3.6/18.63</f>
+        <v>0.19323671497584544</v>
       </c>
       <c r="D1284" t="s">
         <v>721</v>
@@ -29265,7 +29442,7 @@
         <v>723</v>
       </c>
       <c r="F1284" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="1285" spans="1:6" x14ac:dyDescent="0.35">
@@ -29273,11 +29450,11 @@
         <v>874</v>
       </c>
       <c r="B1285" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C1285">
-        <f>3.6/18.63</f>
-        <v>0.19323671497584544</v>
+        <f>-1 * 3.6 / 7.64</f>
+        <v>-0.47120418848167545</v>
       </c>
       <c r="D1285" t="s">
         <v>721</v>
@@ -29286,19 +29463,19 @@
         <v>723</v>
       </c>
       <c r="F1285" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="1286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1286" t="s">
-        <v>875</v>
+        <v>983</v>
       </c>
       <c r="B1286" t="s">
-        <v>846</v>
+        <v>717</v>
       </c>
       <c r="C1286">
-        <f>-1 * 3.6 / 7.64</f>
-        <v>-0.47120418848167545</v>
+        <f>1/10.83</f>
+        <v>9.2336103416435819E-2</v>
       </c>
       <c r="D1286" t="s">
         <v>721</v>
@@ -29307,15 +29484,15 @@
         <v>723</v>
       </c>
       <c r="F1286" t="s">
-        <v>1016</v>
+        <v>984</v>
       </c>
     </row>
     <row r="1287" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1287" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B1287" t="s">
-        <v>717</v>
+        <v>845</v>
       </c>
       <c r="C1287">
         <f>1/10.83</f>
@@ -29328,15 +29505,15 @@
         <v>723</v>
       </c>
       <c r="F1287" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="1288" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1288" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B1288" t="s">
-        <v>846</v>
+        <v>717</v>
       </c>
       <c r="C1288">
         <f>1/10.83</f>
@@ -29349,15 +29526,15 @@
         <v>723</v>
       </c>
       <c r="F1288" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="1289" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1289" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B1289" t="s">
-        <v>717</v>
+        <v>845</v>
       </c>
       <c r="C1289">
         <f>1/10.83</f>
@@ -29370,7 +29547,7 @@
         <v>723</v>
       </c>
       <c r="F1289" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="1290" spans="1:6" x14ac:dyDescent="0.35">
@@ -29378,79 +29555,75 @@
         <v>986</v>
       </c>
       <c r="B1290" t="s">
-        <v>846</v>
-      </c>
-      <c r="C1290">
-        <f>1/10.83</f>
-        <v>9.2336103416435819E-2</v>
+        <v>718</v>
+      </c>
+      <c r="C1290" s="2">
+        <f>8760 * 0.7 / (7200 * 1000000)</f>
+        <v>8.5166666666666663E-7</v>
       </c>
       <c r="D1290" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E1290" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="F1290" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="1291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1291" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B1291" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1291" s="2">
+        <v>719</v>
+      </c>
+      <c r="C1291">
+        <v>1</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>729</v>
+      </c>
+      <c r="E1291" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1292" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>718</v>
+      </c>
+      <c r="C1292" s="2">
         <f>8760 * 0.7 / (7200 * 1000000)</f>
         <v>8.5166666666666663E-7</v>
       </c>
-      <c r="D1291" t="s">
-        <v>722</v>
-      </c>
-      <c r="E1291" t="s">
+      <c r="D1292" t="s">
+        <v>722</v>
+      </c>
+      <c r="E1292" t="s">
         <v>733</v>
       </c>
-      <c r="F1291" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="1292" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1292" t="s">
+      <c r="F1292" t="s">
         <v>987</v>
-      </c>
-      <c r="B1292" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1292">
-        <v>1</v>
-      </c>
-      <c r="D1292" t="s">
-        <v>729</v>
-      </c>
-      <c r="E1292" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="1293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1293" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B1293" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1293" s="2">
-        <f>8760 * 0.7 / (7200 * 1000000)</f>
-        <v>8.5166666666666663E-7</v>
+        <v>719</v>
+      </c>
+      <c r="C1293">
+        <v>1</v>
       </c>
       <c r="D1293" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E1293" t="s">
-        <v>733</v>
-      </c>
-      <c r="F1293" t="s">
-        <v>988</v>
+        <v>729</v>
       </c>
     </row>
     <row r="1294" spans="1:6" x14ac:dyDescent="0.35">
@@ -29458,75 +29631,75 @@
         <v>989</v>
       </c>
       <c r="B1294" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1294">
-        <v>1</v>
+        <v>718</v>
+      </c>
+      <c r="C1294" s="2">
+        <f>8760 * 0.48 / (4100 * 1000000)</f>
+        <v>1.0255609756097561E-6</v>
       </c>
       <c r="D1294" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="E1294" t="s">
-        <v>729</v>
+        <v>733</v>
+      </c>
+      <c r="F1294" t="s">
+        <v>990</v>
       </c>
     </row>
     <row r="1295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1295" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B1295" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1295" s="2">
+        <v>719</v>
+      </c>
+      <c r="C1295">
+        <v>1</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>729</v>
+      </c>
+      <c r="E1295" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1296" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>718</v>
+      </c>
+      <c r="C1296" s="2">
         <f>8760 * 0.48 / (4100 * 1000000)</f>
         <v>1.0255609756097561E-6</v>
       </c>
-      <c r="D1295" t="s">
-        <v>722</v>
-      </c>
-      <c r="E1295" t="s">
+      <c r="D1296" t="s">
+        <v>722</v>
+      </c>
+      <c r="E1296" t="s">
         <v>733</v>
       </c>
-      <c r="F1295" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="1296" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1296" t="s">
+      <c r="F1296" t="s">
         <v>990</v>
-      </c>
-      <c r="B1296" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1296">
-        <v>1</v>
-      </c>
-      <c r="D1296" t="s">
-        <v>729</v>
-      </c>
-      <c r="E1296" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="1297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1297" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B1297" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1297" s="2">
-        <f>8760 * 0.48 / (4100 * 1000000)</f>
-        <v>1.0255609756097561E-6</v>
+        <v>719</v>
+      </c>
+      <c r="C1297">
+        <v>1</v>
       </c>
       <c r="D1297" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E1297" t="s">
-        <v>733</v>
-      </c>
-      <c r="F1297" t="s">
-        <v>991</v>
+        <v>729</v>
       </c>
     </row>
     <row r="1298" spans="1:6" x14ac:dyDescent="0.35">
@@ -29534,75 +29707,75 @@
         <v>992</v>
       </c>
       <c r="B1298" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1298">
-        <v>1</v>
+        <v>718</v>
+      </c>
+      <c r="C1298" s="2">
+        <f>8760 * 0.53 / (5100 * 1000000)</f>
+        <v>9.103529411764706E-7</v>
       </c>
       <c r="D1298" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="E1298" t="s">
-        <v>729</v>
+        <v>733</v>
+      </c>
+      <c r="F1298" t="s">
+        <v>993</v>
       </c>
     </row>
     <row r="1299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1299" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B1299" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1299" s="2">
+        <v>719</v>
+      </c>
+      <c r="C1299">
+        <v>1</v>
+      </c>
+      <c r="D1299" t="s">
+        <v>729</v>
+      </c>
+      <c r="E1299" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1300" t="s">
+        <v>994</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>718</v>
+      </c>
+      <c r="C1300" s="2">
         <f>8760 * 0.53 / (5100 * 1000000)</f>
         <v>9.103529411764706E-7</v>
       </c>
-      <c r="D1299" t="s">
-        <v>722</v>
-      </c>
-      <c r="E1299" t="s">
+      <c r="D1300" t="s">
+        <v>722</v>
+      </c>
+      <c r="E1300" t="s">
         <v>733</v>
       </c>
-      <c r="F1299" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="1300" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1300" t="s">
+      <c r="F1300" t="s">
         <v>993</v>
-      </c>
-      <c r="B1300" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1300">
-        <v>1</v>
-      </c>
-      <c r="D1300" t="s">
-        <v>729</v>
-      </c>
-      <c r="E1300" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="1301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1301" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B1301" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1301" s="2">
-        <f>8760 * 0.53 / (5100 * 1000000)</f>
-        <v>9.103529411764706E-7</v>
+        <v>719</v>
+      </c>
+      <c r="C1301">
+        <v>1</v>
       </c>
       <c r="D1301" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E1301" t="s">
-        <v>733</v>
-      </c>
-      <c r="F1301" t="s">
-        <v>994</v>
+        <v>729</v>
       </c>
     </row>
     <row r="1302" spans="1:6" x14ac:dyDescent="0.35">
@@ -29610,37 +29783,37 @@
         <v>995</v>
       </c>
       <c r="B1302" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1302">
-        <v>1</v>
+        <v>718</v>
+      </c>
+      <c r="C1302" s="2">
+        <f>8760 * 0.7 / (7200 * 1000000)</f>
+        <v>8.5166666666666663E-7</v>
       </c>
       <c r="D1302" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="E1302" t="s">
-        <v>729</v>
+        <v>733</v>
+      </c>
+      <c r="F1302" t="s">
+        <v>987</v>
       </c>
     </row>
     <row r="1303" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1303" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B1303" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1303" s="2">
-        <f>8760 * 0.7 / (7200 * 1000000)</f>
-        <v>8.5166666666666663E-7</v>
+        <v>719</v>
+      </c>
+      <c r="C1303">
+        <v>1</v>
       </c>
       <c r="D1303" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E1303" t="s">
-        <v>733</v>
-      </c>
-      <c r="F1303" t="s">
-        <v>988</v>
+        <v>729</v>
       </c>
     </row>
     <row r="1304" spans="1:6" x14ac:dyDescent="0.35">
@@ -29648,37 +29821,37 @@
         <v>996</v>
       </c>
       <c r="B1304" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1304">
-        <v>1</v>
+        <v>718</v>
+      </c>
+      <c r="C1304" s="2">
+        <f>8760 * 0.7 / (7200 * 1000000)</f>
+        <v>8.5166666666666663E-7</v>
       </c>
       <c r="D1304" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="E1304" t="s">
-        <v>729</v>
+        <v>733</v>
+      </c>
+      <c r="F1304" t="s">
+        <v>987</v>
       </c>
     </row>
     <row r="1305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1305" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B1305" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1305" s="2">
-        <f>8760 * 0.7 / (7200 * 1000000)</f>
-        <v>8.5166666666666663E-7</v>
+        <v>719</v>
+      </c>
+      <c r="C1305">
+        <v>1</v>
       </c>
       <c r="D1305" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E1305" t="s">
-        <v>733</v>
-      </c>
-      <c r="F1305" t="s">
-        <v>988</v>
+        <v>729</v>
       </c>
     </row>
     <row r="1306" spans="1:6" x14ac:dyDescent="0.35">
@@ -29686,37 +29859,37 @@
         <v>997</v>
       </c>
       <c r="B1306" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1306">
-        <v>1</v>
+        <v>718</v>
+      </c>
+      <c r="C1306" s="2">
+        <f>8760 * 0.48 / (4100 * 1000000)</f>
+        <v>1.0255609756097561E-6</v>
       </c>
       <c r="D1306" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="E1306" t="s">
-        <v>729</v>
+        <v>733</v>
+      </c>
+      <c r="F1306" t="s">
+        <v>990</v>
       </c>
     </row>
     <row r="1307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1307" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B1307" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1307" s="2">
-        <f>8760 * 0.48 / (4100 * 1000000)</f>
-        <v>1.0255609756097561E-6</v>
+        <v>719</v>
+      </c>
+      <c r="C1307">
+        <v>1</v>
       </c>
       <c r="D1307" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E1307" t="s">
-        <v>733</v>
-      </c>
-      <c r="F1307" t="s">
-        <v>991</v>
+        <v>729</v>
       </c>
     </row>
     <row r="1308" spans="1:6" x14ac:dyDescent="0.35">
@@ -29724,37 +29897,37 @@
         <v>998</v>
       </c>
       <c r="B1308" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1308">
-        <v>1</v>
+        <v>718</v>
+      </c>
+      <c r="C1308" s="2">
+        <f>8760 * 0.48 / (4100 * 1000000)</f>
+        <v>1.0255609756097561E-6</v>
       </c>
       <c r="D1308" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="E1308" t="s">
-        <v>729</v>
+        <v>733</v>
+      </c>
+      <c r="F1308" t="s">
+        <v>990</v>
       </c>
     </row>
     <row r="1309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1309" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B1309" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1309" s="2">
-        <f>8760 * 0.48 / (4100 * 1000000)</f>
-        <v>1.0255609756097561E-6</v>
+        <v>719</v>
+      </c>
+      <c r="C1309">
+        <v>1</v>
       </c>
       <c r="D1309" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E1309" t="s">
-        <v>733</v>
-      </c>
-      <c r="F1309" t="s">
-        <v>991</v>
+        <v>729</v>
       </c>
     </row>
     <row r="1310" spans="1:6" x14ac:dyDescent="0.35">
@@ -29762,37 +29935,37 @@
         <v>999</v>
       </c>
       <c r="B1310" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1310">
-        <v>1</v>
+        <v>718</v>
+      </c>
+      <c r="C1310" s="2">
+        <f>8760 * 0.53 / (5100 * 1000000)</f>
+        <v>9.103529411764706E-7</v>
       </c>
       <c r="D1310" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="E1310" t="s">
-        <v>729</v>
+        <v>733</v>
+      </c>
+      <c r="F1310" t="s">
+        <v>993</v>
       </c>
     </row>
     <row r="1311" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1311" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B1311" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1311" s="2">
-        <f>8760 * 0.53 / (5100 * 1000000)</f>
-        <v>9.103529411764706E-7</v>
+        <v>719</v>
+      </c>
+      <c r="C1311">
+        <v>1</v>
       </c>
       <c r="D1311" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E1311" t="s">
-        <v>733</v>
-      </c>
-      <c r="F1311" t="s">
-        <v>994</v>
+        <v>729</v>
       </c>
     </row>
     <row r="1312" spans="1:6" x14ac:dyDescent="0.35">
@@ -29800,42 +29973,42 @@
         <v>1000</v>
       </c>
       <c r="B1312" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1312">
-        <v>1</v>
-      </c>
-      <c r="D1312" t="s">
-        <v>729</v>
-      </c>
-      <c r="E1312" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="1313" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1313" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B1313" t="s">
-        <v>718</v>
-      </c>
-      <c r="C1313" s="2">
+        <v>718</v>
+      </c>
+      <c r="C1312" s="2">
         <f>8760 * 0.53 / (5100 * 1000000)</f>
         <v>9.103529411764706E-7</v>
       </c>
+      <c r="D1312" t="s">
+        <v>722</v>
+      </c>
+      <c r="E1312" t="s">
+        <v>733</v>
+      </c>
+      <c r="F1312" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1313" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>719</v>
+      </c>
+      <c r="C1313" s="3">
+        <v>1</v>
+      </c>
       <c r="D1313" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="E1313" t="s">
-        <v>733</v>
-      </c>
-      <c r="F1313" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="1314" spans="1:6" x14ac:dyDescent="0.35">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1314" t="s">
-        <v>1001</v>
+        <v>1017</v>
       </c>
       <c r="B1314" t="s">
         <v>719</v>
@@ -29844,15 +30017,15 @@
         <v>1</v>
       </c>
       <c r="D1314" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="E1314" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="1315" spans="1:6" x14ac:dyDescent="0.35">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1315" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B1315" t="s">
         <v>719</v>
@@ -29867,7 +30040,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="1316" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1316" t="s">
         <v>1020</v>
       </c>
@@ -29884,7 +30057,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="1317" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1317" t="s">
         <v>1021</v>
       </c>
@@ -29901,9 +30074,9 @@
         <v>721</v>
       </c>
     </row>
-    <row r="1318" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1318" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="B1318" t="s">
         <v>719</v>
@@ -29918,25 +30091,8 @@
         <v>721</v>
       </c>
     </row>
-    <row r="1319" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1319" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B1319" t="s">
-        <v>719</v>
-      </c>
-      <c r="C1319" s="3">
-        <v>1</v>
-      </c>
-      <c r="D1319" t="s">
-        <v>721</v>
-      </c>
-      <c r="E1319" t="s">
-        <v>721</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F1319" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F1318" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>